--- a/eduservices/tagetik/RAPPORT_ALLOUE_DEPLIABLE.xlsx
+++ b/eduservices/tagetik/RAPPORT_ALLOUE_DEPLIABLE.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="P&amp;L chargé dépliable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Avant-Après allocation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,11 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0;-#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="-0.0;-0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,7 +44,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -59,12 +60,32 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="007D8B98"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B3641C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="0051606D"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00152230"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="007D8B98"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B3641C"/>
       <sz val="9"/>
     </font>
     <font>
@@ -82,7 +103,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="000D7A62"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -149,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,7 +189,19 @@
     <xf numFmtId="3" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -180,19 +213,37 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -201,50 +252,68 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="4"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -610,28 +679,31 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>P&amp;L CHARGÉ — DÉPLIABLE À TOUS LES NIVEAUX  ·  2026</t>
+          <t>LE CHOC DE L'ALLOCATION — dépliable à tous les niveaux  ·  2026</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Après allocation : la marge à n'importe quelle maille. Coûts chargés ventilés à l'effectif (clé du cadrage). Marque → Campus → Programme → Année → Modalité.</t>
+          <t>EBITDA propre (avec SES coûts) → on charge la quote-part de siège → EBITDA net. Le Δ = ce que le siège coûte à la maille. Clé = effectif.</t>
         </is>
       </c>
     </row>
@@ -648,22 +720,37 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Effectif</t>
+          <t>Eff.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Coût chargé</t>
+          <t>EBITDA propre</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>% pr.</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>− Q-part siège</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>EBITDA net</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Marge</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>% net</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Δ (pt)</t>
         </is>
       </c>
     </row>
@@ -679,1158 +766,1635 @@
       <c r="C5" s="7" t="n">
         <v>1249</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>-7858779</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="D5" s="8" t="n">
+        <v>3176674</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.332029155088788</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>-1467998</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1708676</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="H5" s="11" t="n">
         <v>0.1785925824284567</v>
       </c>
+      <c r="I5" s="12" t="n">
+        <v>-15.34365726603313</v>
+      </c>
     </row>
     <row r="6" hidden="1" outlineLevel="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="14" t="n">
         <v>1773610</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="15" t="n">
         <v>249</v>
       </c>
-      <c r="D6" s="10" t="n">
-        <v>-1410693</v>
-      </c>
-      <c r="E6" s="12" t="n">
+      <c r="D6" s="14" t="n">
+        <v>655576</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.3696280467521045</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>-292659</v>
+      </c>
+      <c r="G6" s="18" t="n">
         <v>362917</v>
       </c>
-      <c r="F6" s="13" t="n">
-        <v>0.2046203899182152</v>
+      <c r="H6" s="19" t="n">
+        <v>0.2046203899182153</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>-16.50076568338892</v>
       </c>
     </row>
     <row r="7" hidden="1" outlineLevel="2">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>BAC_MGT</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="22" t="n">
         <v>1034245</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="23" t="n">
         <v>148</v>
       </c>
-      <c r="D7" s="15" t="n">
-        <v>-838484</v>
-      </c>
-      <c r="E7" s="17" t="n">
+      <c r="D7" s="24" t="n">
+        <v>369711</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>0.3574692021133862</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>-173950</v>
+      </c>
+      <c r="G7" s="27" t="n">
         <v>195761</v>
       </c>
-      <c r="F7" s="18" t="n">
-        <v>0.1892788172832639</v>
+      <c r="H7" s="28" t="n">
+        <v>0.189278817283264</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>-16.81903848301222</v>
       </c>
     </row>
     <row r="8" hidden="1" outlineLevel="3">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="31" t="n">
         <v>375615</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="32" t="n">
         <v>51</v>
       </c>
-      <c r="D8" s="20" t="n">
-        <v>-288937</v>
-      </c>
-      <c r="E8" s="17" t="n">
+      <c r="D8" s="24" t="n">
+        <v>146620</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>0.3903467229406424</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>-59942</v>
+      </c>
+      <c r="G8" s="27" t="n">
         <v>86678</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="H8" s="28" t="n">
         <v>0.2307624359012947</v>
       </c>
+      <c r="I8" s="29" t="n">
+        <v>-15.95842870393477</v>
+      </c>
     </row>
     <row r="9" hidden="1" outlineLevel="4">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="31" t="n">
         <v>375615</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="32" t="n">
         <v>51</v>
       </c>
-      <c r="D9" s="20" t="n">
-        <v>-288937</v>
-      </c>
-      <c r="E9" s="17" t="n">
+      <c r="D9" s="24" t="n">
+        <v>146620</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>0.3903467229406424</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>-59942</v>
+      </c>
+      <c r="G9" s="27" t="n">
         <v>86678</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="H9" s="28" t="n">
         <v>0.2307624359012947</v>
       </c>
+      <c r="I9" s="29" t="n">
+        <v>-15.95842870393477</v>
+      </c>
     </row>
     <row r="10" hidden="1" outlineLevel="3">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="31" t="n">
         <v>332710</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="32" t="n">
         <v>49</v>
       </c>
-      <c r="D10" s="20" t="n">
-        <v>-277606</v>
-      </c>
-      <c r="E10" s="17" t="n">
+      <c r="D10" s="24" t="n">
+        <v>112695</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>0.3387192362971769</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>-57592</v>
+      </c>
+      <c r="G10" s="27" t="n">
         <v>55104</v>
       </c>
-      <c r="F10" s="18" t="n">
-        <v>0.1656208159665738</v>
+      <c r="H10" s="28" t="n">
+        <v>0.1656208159665737</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>-17.30984203306032</v>
       </c>
     </row>
     <row r="11" hidden="1" outlineLevel="4">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="31" t="n">
         <v>332710</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="32" t="n">
         <v>49</v>
       </c>
-      <c r="D11" s="20" t="n">
-        <v>-277606</v>
-      </c>
-      <c r="E11" s="17" t="n">
+      <c r="D11" s="24" t="n">
+        <v>112695</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>0.3387192362971769</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>-57592</v>
+      </c>
+      <c r="G11" s="27" t="n">
         <v>55104</v>
       </c>
-      <c r="F11" s="18" t="n">
-        <v>0.1656208159665738</v>
+      <c r="H11" s="28" t="n">
+        <v>0.1656208159665737</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>-17.30984203306032</v>
       </c>
     </row>
     <row r="12" hidden="1" outlineLevel="3">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="31" t="n">
         <v>325920</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="32" t="n">
         <v>48</v>
       </c>
-      <c r="D12" s="20" t="n">
-        <v>-271941</v>
-      </c>
-      <c r="E12" s="17" t="n">
+      <c r="D12" s="24" t="n">
+        <v>110395</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>0.3387192362971769</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>-56416</v>
+      </c>
+      <c r="G12" s="27" t="n">
         <v>53979</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="H12" s="28" t="n">
         <v>0.1656208159665737</v>
       </c>
+      <c r="I12" s="29" t="n">
+        <v>-17.30984203306032</v>
+      </c>
     </row>
     <row r="13" hidden="1" outlineLevel="4">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="31" t="n">
         <v>325920</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="32" t="n">
         <v>48</v>
       </c>
-      <c r="D13" s="20" t="n">
-        <v>-271941</v>
-      </c>
-      <c r="E13" s="17" t="n">
+      <c r="D13" s="24" t="n">
+        <v>110395</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>0.3387192362971769</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>-56416</v>
+      </c>
+      <c r="G13" s="27" t="n">
         <v>53979</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="H13" s="28" t="n">
         <v>0.1656208159665737</v>
       </c>
+      <c r="I13" s="29" t="n">
+        <v>-17.30984203306032</v>
+      </c>
     </row>
     <row r="14" hidden="1" outlineLevel="2">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>MAS_MGT</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="22" t="n">
         <v>739365</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="23" t="n">
         <v>101</v>
       </c>
-      <c r="D14" s="15" t="n">
-        <v>-572209</v>
-      </c>
-      <c r="E14" s="17" t="n">
+      <c r="D14" s="24" t="n">
+        <v>285865</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0.3866361878912864</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>-118709</v>
+      </c>
+      <c r="G14" s="27" t="n">
         <v>167156</v>
       </c>
-      <c r="F14" s="18" t="n">
-        <v>0.2260806224012721</v>
+      <c r="H14" s="28" t="n">
+        <v>0.2260806224012722</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>-16.05555654900142</v>
       </c>
     </row>
     <row r="15" hidden="1" outlineLevel="3">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="31" t="n">
         <v>375615</v>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="32" t="n">
         <v>51</v>
       </c>
-      <c r="D15" s="20" t="n">
-        <v>-288937</v>
-      </c>
-      <c r="E15" s="17" t="n">
+      <c r="D15" s="24" t="n">
+        <v>146620</v>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>0.3903467229406424</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>-59942</v>
+      </c>
+      <c r="G15" s="27" t="n">
         <v>86678</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="H15" s="28" t="n">
         <v>0.2307624359012947</v>
       </c>
+      <c r="I15" s="29" t="n">
+        <v>-15.95842870393477</v>
+      </c>
     </row>
     <row r="16" hidden="1" outlineLevel="4">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="31" t="n">
         <v>375615</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="32" t="n">
         <v>51</v>
       </c>
-      <c r="D16" s="20" t="n">
-        <v>-288937</v>
-      </c>
-      <c r="E16" s="17" t="n">
+      <c r="D16" s="24" t="n">
+        <v>146620</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>0.3903467229406424</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>-59942</v>
+      </c>
+      <c r="G16" s="27" t="n">
         <v>86678</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="H16" s="28" t="n">
         <v>0.2307624359012947</v>
       </c>
+      <c r="I16" s="29" t="n">
+        <v>-15.95842870393477</v>
+      </c>
     </row>
     <row r="17" hidden="1" outlineLevel="3">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="31" t="n">
         <v>363750</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="D17" s="20" t="n">
-        <v>-283272</v>
-      </c>
-      <c r="E17" s="17" t="n">
+      <c r="D17" s="24" t="n">
+        <v>139245</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>0.3828046205440317</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>-58767</v>
+      </c>
+      <c r="G17" s="27" t="n">
         <v>80478</v>
       </c>
-      <c r="F17" s="18" t="n">
-        <v>0.2212460949021355</v>
+      <c r="H17" s="28" t="n">
+        <v>0.2212460949021354</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>-16.15585256418963</v>
       </c>
     </row>
     <row r="18" hidden="1" outlineLevel="4">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="31" t="n">
         <v>363750</v>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="D18" s="20" t="n">
-        <v>-283272</v>
-      </c>
-      <c r="E18" s="17" t="n">
+      <c r="D18" s="24" t="n">
+        <v>139245</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>0.3828046205440317</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>-58767</v>
+      </c>
+      <c r="G18" s="27" t="n">
         <v>80478</v>
       </c>
-      <c r="F18" s="18" t="n">
-        <v>0.2212460949021355</v>
+      <c r="H18" s="28" t="n">
+        <v>0.2212460949021354</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>-16.15585256418963</v>
       </c>
     </row>
     <row r="19" hidden="1" outlineLevel="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="14" t="n">
         <v>2496705</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="15" t="n">
         <v>324</v>
       </c>
-      <c r="D19" s="10" t="n">
-        <v>-1920529</v>
-      </c>
-      <c r="E19" s="12" t="n">
+      <c r="D19" s="14" t="n">
+        <v>956986</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.3832995888581151</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>-380810</v>
+      </c>
+      <c r="G19" s="18" t="n">
         <v>576176</v>
       </c>
-      <c r="F19" s="13" t="n">
-        <v>0.2307747207657637</v>
+      <c r="H19" s="19" t="n">
+        <v>0.2307747207657639</v>
+      </c>
+      <c r="I19" s="20" t="n">
+        <v>-15.25248680923512</v>
       </c>
     </row>
     <row r="20" hidden="1" outlineLevel="2">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>BAC_MGT</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="22" t="n">
         <v>1459140</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="23" t="n">
         <v>193</v>
       </c>
-      <c r="D20" s="15" t="n">
-        <v>-1144019</v>
-      </c>
-      <c r="E20" s="17" t="n">
+      <c r="D20" s="24" t="n">
+        <v>541962</v>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>0.3714254333306767</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <v>-226840</v>
+      </c>
+      <c r="G20" s="27" t="n">
         <v>315121</v>
       </c>
-      <c r="F20" s="18" t="n">
-        <v>0.2159638005259796</v>
+      <c r="H20" s="28" t="n">
+        <v>0.2159638005259797</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>-15.5461632804697</v>
       </c>
     </row>
     <row r="21" hidden="1" outlineLevel="3">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
+      <c r="B21" s="31" t="n">
         <v>525690</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="32" t="n">
         <v>66</v>
       </c>
-      <c r="D21" s="20" t="n">
-        <v>-391219</v>
-      </c>
-      <c r="E21" s="17" t="n">
+      <c r="D21" s="24" t="n">
+        <v>212044</v>
+      </c>
+      <c r="E21" s="25" t="n">
+        <v>0.4033623181666706</v>
+      </c>
+      <c r="F21" s="26" t="n">
+        <v>-77572</v>
+      </c>
+      <c r="G21" s="27" t="n">
         <v>134471</v>
       </c>
-      <c r="F21" s="18" t="n">
-        <v>0.2557994463468594</v>
+      <c r="H21" s="28" t="n">
+        <v>0.2557994463468595</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>-14.75628718198111</v>
       </c>
     </row>
     <row r="22" hidden="1" outlineLevel="4">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B22" s="31" t="n">
         <v>525690</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="32" t="n">
         <v>66</v>
       </c>
-      <c r="D22" s="20" t="n">
-        <v>-391219</v>
-      </c>
-      <c r="E22" s="17" t="n">
+      <c r="D22" s="24" t="n">
+        <v>212044</v>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>0.4033623181666706</v>
+      </c>
+      <c r="F22" s="26" t="n">
+        <v>-77572</v>
+      </c>
+      <c r="G22" s="27" t="n">
         <v>134471</v>
       </c>
-      <c r="F22" s="18" t="n">
-        <v>0.2557994463468594</v>
+      <c r="H22" s="28" t="n">
+        <v>0.2557994463468595</v>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>-14.75628718198111</v>
       </c>
     </row>
     <row r="23" hidden="1" outlineLevel="3">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
+      <c r="B23" s="31" t="n">
         <v>470400</v>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="32" t="n">
         <v>64</v>
       </c>
-      <c r="D23" s="20" t="n">
-        <v>-379364</v>
-      </c>
-      <c r="E23" s="17" t="n">
+      <c r="D23" s="24" t="n">
+        <v>166258</v>
+      </c>
+      <c r="E23" s="25" t="n">
+        <v>0.3534395733602083</v>
+      </c>
+      <c r="F23" s="26" t="n">
+        <v>-75222</v>
+      </c>
+      <c r="G23" s="27" t="n">
         <v>91036</v>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="H23" s="28" t="n">
         <v>0.1935296041024129</v>
       </c>
+      <c r="I23" s="29" t="n">
+        <v>-15.99099692577953</v>
+      </c>
     </row>
     <row r="24" hidden="1" outlineLevel="4">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="31" t="n">
         <v>470400</v>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="32" t="n">
         <v>64</v>
       </c>
-      <c r="D24" s="20" t="n">
-        <v>-379364</v>
-      </c>
-      <c r="E24" s="17" t="n">
+      <c r="D24" s="24" t="n">
+        <v>166258</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>0.3534395733602083</v>
+      </c>
+      <c r="F24" s="26" t="n">
+        <v>-75222</v>
+      </c>
+      <c r="G24" s="27" t="n">
         <v>91036</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="H24" s="28" t="n">
         <v>0.1935296041024129</v>
       </c>
+      <c r="I24" s="29" t="n">
+        <v>-15.99099692577953</v>
+      </c>
     </row>
     <row r="25" hidden="1" outlineLevel="3">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="31" t="n">
         <v>463050</v>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="32" t="n">
         <v>63</v>
       </c>
-      <c r="D25" s="20" t="n">
-        <v>-373436</v>
-      </c>
-      <c r="E25" s="17" t="n">
+      <c r="D25" s="24" t="n">
+        <v>163660</v>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>0.3534395733602083</v>
+      </c>
+      <c r="F25" s="26" t="n">
+        <v>-74046</v>
+      </c>
+      <c r="G25" s="27" t="n">
         <v>89614</v>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="H25" s="28" t="n">
         <v>0.1935296041024129</v>
       </c>
+      <c r="I25" s="29" t="n">
+        <v>-15.99099692577954</v>
+      </c>
     </row>
     <row r="26" hidden="1" outlineLevel="4">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="31" t="n">
         <v>463050</v>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="32" t="n">
         <v>63</v>
       </c>
-      <c r="D26" s="20" t="n">
-        <v>-373436</v>
-      </c>
-      <c r="E26" s="17" t="n">
+      <c r="D26" s="24" t="n">
+        <v>163660</v>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>0.3534395733602083</v>
+      </c>
+      <c r="F26" s="26" t="n">
+        <v>-74046</v>
+      </c>
+      <c r="G26" s="27" t="n">
         <v>89614</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="H26" s="28" t="n">
         <v>0.1935296041024129</v>
       </c>
+      <c r="I26" s="29" t="n">
+        <v>-15.99099692577954</v>
+      </c>
     </row>
     <row r="27" hidden="1" outlineLevel="2">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>MAS_MGT</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
+      <c r="B27" s="22" t="n">
         <v>1037565</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="23" t="n">
         <v>131</v>
       </c>
-      <c r="D27" s="15" t="n">
-        <v>-776510</v>
-      </c>
-      <c r="E27" s="17" t="n">
+      <c r="D27" s="24" t="n">
+        <v>415024</v>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>0.3999983550041459</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>-153969</v>
+      </c>
+      <c r="G27" s="27" t="n">
         <v>261055</v>
       </c>
-      <c r="F27" s="18" t="n">
-        <v>0.251603494055802</v>
+      <c r="H27" s="28" t="n">
+        <v>0.2516034940558022</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <v>-14.83948609483437</v>
       </c>
     </row>
     <row r="28" hidden="1" outlineLevel="3">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
+      <c r="B28" s="31" t="n">
         <v>525690</v>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="32" t="n">
         <v>66</v>
       </c>
-      <c r="D28" s="20" t="n">
-        <v>-391219</v>
-      </c>
-      <c r="E28" s="17" t="n">
+      <c r="D28" s="24" t="n">
+        <v>212044</v>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>0.4033623181666706</v>
+      </c>
+      <c r="F28" s="26" t="n">
+        <v>-77572</v>
+      </c>
+      <c r="G28" s="27" t="n">
         <v>134471</v>
       </c>
-      <c r="F28" s="18" t="n">
-        <v>0.2557994463468594</v>
+      <c r="H28" s="28" t="n">
+        <v>0.2557994463468595</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>-14.75628718198111</v>
       </c>
     </row>
     <row r="29" hidden="1" outlineLevel="4">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="31" t="n">
         <v>525690</v>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="32" t="n">
         <v>66</v>
       </c>
-      <c r="D29" s="20" t="n">
-        <v>-391219</v>
-      </c>
-      <c r="E29" s="17" t="n">
+      <c r="D29" s="24" t="n">
+        <v>212044</v>
+      </c>
+      <c r="E29" s="25" t="n">
+        <v>0.4033623181666706</v>
+      </c>
+      <c r="F29" s="26" t="n">
+        <v>-77572</v>
+      </c>
+      <c r="G29" s="27" t="n">
         <v>134471</v>
       </c>
-      <c r="F29" s="18" t="n">
-        <v>0.2557994463468594</v>
+      <c r="H29" s="28" t="n">
+        <v>0.2557994463468595</v>
+      </c>
+      <c r="I29" s="29" t="n">
+        <v>-14.75628718198111</v>
       </c>
     </row>
     <row r="30" hidden="1" outlineLevel="3">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="31" t="n">
         <v>511875</v>
       </c>
-      <c r="C30" s="21" t="n">
+      <c r="C30" s="32" t="n">
         <v>65</v>
       </c>
-      <c r="D30" s="20" t="n">
-        <v>-385291</v>
-      </c>
-      <c r="E30" s="17" t="n">
+      <c r="D30" s="24" t="n">
+        <v>202981</v>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>0.396543601802861</v>
+      </c>
+      <c r="F30" s="26" t="n">
+        <v>-76397</v>
+      </c>
+      <c r="G30" s="27" t="n">
         <v>126584</v>
       </c>
-      <c r="F30" s="18" t="n">
+      <c r="H30" s="28" t="n">
         <v>0.247294297162252</v>
       </c>
+      <c r="I30" s="29" t="n">
+        <v>-14.9249304640609</v>
+      </c>
     </row>
     <row r="31" hidden="1" outlineLevel="4">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
+      <c r="B31" s="31" t="n">
         <v>511875</v>
       </c>
-      <c r="C31" s="21" t="n">
+      <c r="C31" s="32" t="n">
         <v>65</v>
       </c>
-      <c r="D31" s="20" t="n">
-        <v>-385291</v>
-      </c>
-      <c r="E31" s="17" t="n">
+      <c r="D31" s="24" t="n">
+        <v>202981</v>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>0.396543601802861</v>
+      </c>
+      <c r="F31" s="26" t="n">
+        <v>-76397</v>
+      </c>
+      <c r="G31" s="27" t="n">
         <v>126584</v>
       </c>
-      <c r="F31" s="18" t="n">
+      <c r="H31" s="28" t="n">
         <v>0.247294297162252</v>
       </c>
+      <c r="I31" s="29" t="n">
+        <v>-14.9249304640609</v>
+      </c>
     </row>
     <row r="32" hidden="1" outlineLevel="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
+      <c r="B32" s="14" t="n">
         <v>2158300</v>
       </c>
-      <c r="C32" s="11" t="n">
+      <c r="C32" s="15" t="n">
         <v>294</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>-1629079</v>
-      </c>
-      <c r="E32" s="12" t="n">
+      <c r="D32" s="14" t="n">
+        <v>874770</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0.4053051012370847</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>-345549</v>
+      </c>
+      <c r="G32" s="18" t="n">
         <v>529221</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="H32" s="19" t="n">
         <v>0.2452024961454988</v>
       </c>
+      <c r="I32" s="20" t="n">
+        <v>-16.01026050915859</v>
+      </c>
     </row>
     <row r="33" hidden="1" outlineLevel="2">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>BAC_MGT</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
+      <c r="B33" s="22" t="n">
         <v>1260400</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="23" t="n">
         <v>175</v>
       </c>
-      <c r="D33" s="15" t="n">
-        <v>-969690</v>
-      </c>
-      <c r="E33" s="17" t="n">
+      <c r="D33" s="24" t="n">
+        <v>496394</v>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>0.39383850176059</v>
+      </c>
+      <c r="F33" s="26" t="n">
+        <v>-205684</v>
+      </c>
+      <c r="G33" s="27" t="n">
         <v>290710</v>
       </c>
-      <c r="F33" s="18" t="n">
+      <c r="H33" s="28" t="n">
         <v>0.2306488810387246</v>
       </c>
+      <c r="I33" s="29" t="n">
+        <v>-16.31896207218655</v>
+      </c>
     </row>
     <row r="34" hidden="1" outlineLevel="3">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
+      <c r="B34" s="31" t="n">
         <v>455400</v>
       </c>
-      <c r="C34" s="21" t="n">
+      <c r="C34" s="32" t="n">
         <v>60</v>
       </c>
-      <c r="D34" s="20" t="n">
-        <v>-332465</v>
-      </c>
-      <c r="E34" s="17" t="n">
+      <c r="D34" s="24" t="n">
+        <v>193455</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>0.424802595610049</v>
+      </c>
+      <c r="F34" s="26" t="n">
+        <v>-70520</v>
+      </c>
+      <c r="G34" s="27" t="n">
         <v>122935</v>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="H34" s="28" t="n">
         <v>0.2699490680679152</v>
       </c>
+      <c r="I34" s="29" t="n">
+        <v>-15.48535275421338</v>
+      </c>
     </row>
     <row r="35" hidden="1" outlineLevel="4">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
+      <c r="B35" s="31" t="n">
         <v>455400</v>
       </c>
-      <c r="C35" s="21" t="n">
+      <c r="C35" s="32" t="n">
         <v>60</v>
       </c>
-      <c r="D35" s="20" t="n">
-        <v>-332465</v>
-      </c>
-      <c r="E35" s="17" t="n">
+      <c r="D35" s="24" t="n">
+        <v>193455</v>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>0.424802595610049</v>
+      </c>
+      <c r="F35" s="26" t="n">
+        <v>-70520</v>
+      </c>
+      <c r="G35" s="27" t="n">
         <v>122935</v>
       </c>
-      <c r="F35" s="18" t="n">
+      <c r="H35" s="28" t="n">
         <v>0.2699490680679152</v>
       </c>
+      <c r="I35" s="29" t="n">
+        <v>-15.48535275421338</v>
+      </c>
     </row>
     <row r="36" hidden="1" outlineLevel="3">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
+      <c r="B36" s="31" t="n">
         <v>406000</v>
       </c>
-      <c r="C36" s="21" t="n">
+      <c r="C36" s="32" t="n">
         <v>58</v>
       </c>
-      <c r="D36" s="20" t="n">
-        <v>-321383</v>
-      </c>
-      <c r="E36" s="17" t="n">
+      <c r="D36" s="24" t="n">
+        <v>152787</v>
+      </c>
+      <c r="E36" s="25" t="n">
+        <v>0.3763216715257532</v>
+      </c>
+      <c r="F36" s="26" t="n">
+        <v>-68170</v>
+      </c>
+      <c r="G36" s="27" t="n">
         <v>84617</v>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="H36" s="28" t="n">
         <v>0.2084162038050681</v>
       </c>
+      <c r="I36" s="29" t="n">
+        <v>-16.79054677206851</v>
+      </c>
     </row>
     <row r="37" hidden="1" outlineLevel="4">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
+      <c r="B37" s="31" t="n">
         <v>406000</v>
       </c>
-      <c r="C37" s="21" t="n">
+      <c r="C37" s="32" t="n">
         <v>58</v>
       </c>
-      <c r="D37" s="20" t="n">
-        <v>-321383</v>
-      </c>
-      <c r="E37" s="17" t="n">
+      <c r="D37" s="24" t="n">
+        <v>152787</v>
+      </c>
+      <c r="E37" s="25" t="n">
+        <v>0.3763216715257532</v>
+      </c>
+      <c r="F37" s="26" t="n">
+        <v>-68170</v>
+      </c>
+      <c r="G37" s="27" t="n">
         <v>84617</v>
       </c>
-      <c r="F37" s="18" t="n">
+      <c r="H37" s="28" t="n">
         <v>0.2084162038050681</v>
       </c>
+      <c r="I37" s="29" t="n">
+        <v>-16.79054677206851</v>
+      </c>
     </row>
     <row r="38" hidden="1" outlineLevel="3">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
+      <c r="B38" s="31" t="n">
         <v>399000</v>
       </c>
-      <c r="C38" s="21" t="n">
+      <c r="C38" s="32" t="n">
         <v>57</v>
       </c>
-      <c r="D38" s="20" t="n">
-        <v>-315842</v>
-      </c>
-      <c r="E38" s="17" t="n">
+      <c r="D38" s="24" t="n">
+        <v>150152</v>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>0.3763216715257532</v>
+      </c>
+      <c r="F38" s="26" t="n">
+        <v>-66994</v>
+      </c>
+      <c r="G38" s="27" t="n">
         <v>83158</v>
       </c>
-      <c r="F38" s="18" t="n">
+      <c r="H38" s="28" t="n">
         <v>0.2084162038050681</v>
       </c>
+      <c r="I38" s="29" t="n">
+        <v>-16.79054677206851</v>
+      </c>
     </row>
     <row r="39" hidden="1" outlineLevel="4">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n">
+      <c r="B39" s="31" t="n">
         <v>399000</v>
       </c>
-      <c r="C39" s="21" t="n">
+      <c r="C39" s="32" t="n">
         <v>57</v>
       </c>
-      <c r="D39" s="20" t="n">
-        <v>-315842</v>
-      </c>
-      <c r="E39" s="17" t="n">
+      <c r="D39" s="24" t="n">
+        <v>150152</v>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>0.3763216715257532</v>
+      </c>
+      <c r="F39" s="26" t="n">
+        <v>-66994</v>
+      </c>
+      <c r="G39" s="27" t="n">
         <v>83158</v>
       </c>
-      <c r="F39" s="18" t="n">
+      <c r="H39" s="28" t="n">
         <v>0.2084162038050681</v>
       </c>
+      <c r="I39" s="29" t="n">
+        <v>-16.79054677206851</v>
+      </c>
     </row>
     <row r="40" hidden="1" outlineLevel="2">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>MAS_MGT</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
+      <c r="B40" s="22" t="n">
         <v>897900</v>
       </c>
-      <c r="C40" s="16" t="n">
+      <c r="C40" s="23" t="n">
         <v>119</v>
       </c>
-      <c r="D40" s="15" t="n">
-        <v>-659389</v>
-      </c>
-      <c r="E40" s="17" t="n">
+      <c r="D40" s="24" t="n">
+        <v>378376</v>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>0.4214009938533828</v>
+      </c>
+      <c r="F40" s="26" t="n">
+        <v>-139865</v>
+      </c>
+      <c r="G40" s="27" t="n">
         <v>238511</v>
       </c>
-      <c r="F40" s="18" t="n">
-        <v>0.2656316936959813</v>
+      <c r="H40" s="28" t="n">
+        <v>0.2656316936959814</v>
+      </c>
+      <c r="I40" s="29" t="n">
+        <v>-15.57693001574014</v>
       </c>
     </row>
     <row r="41" hidden="1" outlineLevel="3">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n">
+      <c r="B41" s="31" t="n">
         <v>455400</v>
       </c>
-      <c r="C41" s="21" t="n">
+      <c r="C41" s="32" t="n">
         <v>60</v>
       </c>
-      <c r="D41" s="20" t="n">
-        <v>-332465</v>
-      </c>
-      <c r="E41" s="17" t="n">
+      <c r="D41" s="24" t="n">
+        <v>193455</v>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>0.424802595610049</v>
+      </c>
+      <c r="F41" s="26" t="n">
+        <v>-70520</v>
+      </c>
+      <c r="G41" s="27" t="n">
         <v>122935</v>
       </c>
-      <c r="F41" s="18" t="n">
+      <c r="H41" s="28" t="n">
         <v>0.2699490680679152</v>
       </c>
+      <c r="I41" s="29" t="n">
+        <v>-15.48535275421338</v>
+      </c>
     </row>
     <row r="42" hidden="1" outlineLevel="4">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B42" s="20" t="n">
+      <c r="B42" s="31" t="n">
         <v>455400</v>
       </c>
-      <c r="C42" s="21" t="n">
+      <c r="C42" s="32" t="n">
         <v>60</v>
       </c>
-      <c r="D42" s="20" t="n">
-        <v>-332465</v>
-      </c>
-      <c r="E42" s="17" t="n">
+      <c r="D42" s="24" t="n">
+        <v>193455</v>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>0.424802595610049</v>
+      </c>
+      <c r="F42" s="26" t="n">
+        <v>-70520</v>
+      </c>
+      <c r="G42" s="27" t="n">
         <v>122935</v>
       </c>
-      <c r="F42" s="18" t="n">
+      <c r="H42" s="28" t="n">
         <v>0.2699490680679152</v>
       </c>
+      <c r="I42" s="29" t="n">
+        <v>-15.48535275421338</v>
+      </c>
     </row>
     <row r="43" hidden="1" outlineLevel="3">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n">
+      <c r="B43" s="31" t="n">
         <v>442500</v>
       </c>
-      <c r="C43" s="21" t="n">
+      <c r="C43" s="32" t="n">
         <v>59</v>
       </c>
-      <c r="D43" s="20" t="n">
-        <v>-326924</v>
-      </c>
-      <c r="E43" s="17" t="n">
+      <c r="D43" s="24" t="n">
+        <v>184921</v>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>0.4179002267573697</v>
+      </c>
+      <c r="F43" s="26" t="n">
+        <v>-69345</v>
+      </c>
+      <c r="G43" s="27" t="n">
         <v>115576</v>
       </c>
-      <c r="F43" s="18" t="n">
-        <v>0.2611884568847301</v>
+      <c r="H43" s="28" t="n">
+        <v>0.2611884568847302</v>
+      </c>
+      <c r="I43" s="29" t="n">
+        <v>-15.67117698726395</v>
       </c>
     </row>
     <row r="44" hidden="1" outlineLevel="4">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n">
+      <c r="B44" s="31" t="n">
         <v>442500</v>
       </c>
-      <c r="C44" s="21" t="n">
+      <c r="C44" s="32" t="n">
         <v>59</v>
       </c>
-      <c r="D44" s="20" t="n">
-        <v>-326924</v>
-      </c>
-      <c r="E44" s="17" t="n">
+      <c r="D44" s="24" t="n">
+        <v>184921</v>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>0.4179002267573697</v>
+      </c>
+      <c r="F44" s="26" t="n">
+        <v>-69345</v>
+      </c>
+      <c r="G44" s="27" t="n">
         <v>115576</v>
       </c>
-      <c r="F44" s="18" t="n">
-        <v>0.2611884568847301</v>
+      <c r="H44" s="28" t="n">
+        <v>0.2611884568847302</v>
+      </c>
+      <c r="I44" s="29" t="n">
+        <v>-15.67117698726395</v>
       </c>
     </row>
     <row r="45" hidden="1" outlineLevel="1">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n">
+      <c r="B45" s="14" t="n">
         <v>3138840</v>
       </c>
-      <c r="C45" s="11" t="n">
+      <c r="C45" s="15" t="n">
         <v>382</v>
       </c>
-      <c r="D45" s="10" t="n">
-        <v>-2898477</v>
-      </c>
-      <c r="E45" s="12" t="n">
+      <c r="D45" s="14" t="n">
+        <v>689342</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0.2196168011112385</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>-448979</v>
+      </c>
+      <c r="G45" s="18" t="n">
         <v>240363</v>
       </c>
-      <c r="F45" s="13" t="n">
-        <v>0.07657694540495476</v>
+      <c r="H45" s="19" t="n">
+        <v>0.0765769454049547</v>
+      </c>
+      <c r="I45" s="20" t="n">
+        <v>-14.30398557062839</v>
       </c>
     </row>
     <row r="46" hidden="1" outlineLevel="2">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>BAC_MGT</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
+      <c r="B46" s="22" t="n">
         <v>1838220</v>
       </c>
-      <c r="C46" s="16" t="n">
+      <c r="C46" s="23" t="n">
         <v>228</v>
       </c>
-      <c r="D46" s="15" t="n">
-        <v>-1729981</v>
-      </c>
-      <c r="E46" s="17" t="n">
+      <c r="D46" s="24" t="n">
+        <v>376216</v>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>0.2046631840123507</v>
+      </c>
+      <c r="F46" s="26" t="n">
+        <v>-267977</v>
+      </c>
+      <c r="G46" s="27" t="n">
         <v>108239</v>
       </c>
-      <c r="F46" s="18" t="n">
-        <v>0.05888241431002268</v>
+      <c r="H46" s="28" t="n">
+        <v>0.05888241431002265</v>
+      </c>
+      <c r="I46" s="29" t="n">
+        <v>-14.57807697023281</v>
       </c>
     </row>
     <row r="47" hidden="1" outlineLevel="3">
-      <c r="A47" s="19" t="inlineStr">
+      <c r="A47" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B47" s="20" t="n">
+      <c r="B47" s="31" t="n">
         <v>662220</v>
       </c>
-      <c r="C47" s="21" t="n">
+      <c r="C47" s="32" t="n">
         <v>78</v>
       </c>
-      <c r="D47" s="20" t="n">
-        <v>-591836</v>
-      </c>
-      <c r="E47" s="17" t="n">
+      <c r="D47" s="24" t="n">
+        <v>162061</v>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>0.2447233887727477</v>
+      </c>
+      <c r="F47" s="26" t="n">
+        <v>-91676</v>
+      </c>
+      <c r="G47" s="27" t="n">
         <v>70384</v>
       </c>
-      <c r="F47" s="18" t="n">
+      <c r="H47" s="28" t="n">
         <v>0.1062854295212995</v>
       </c>
+      <c r="I47" s="29" t="n">
+        <v>-13.84379592514482</v>
+      </c>
     </row>
     <row r="48" hidden="1" outlineLevel="4">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="33" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="B48" s="20" t="n">
+      <c r="B48" s="31" t="n">
         <v>662220</v>
       </c>
-      <c r="C48" s="21" t="n">
+      <c r="C48" s="32" t="n">
         <v>78</v>
       </c>
-      <c r="D48" s="20" t="n">
-        <v>-591836</v>
-      </c>
-      <c r="E48" s="17" t="n">
+      <c r="D48" s="24" t="n">
+        <v>162061</v>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>0.2447233887727477</v>
+      </c>
+      <c r="F48" s="26" t="n">
+        <v>-91676</v>
+      </c>
+      <c r="G48" s="27" t="n">
         <v>70384</v>
       </c>
-      <c r="F48" s="18" t="n">
+      <c r="H48" s="28" t="n">
         <v>0.1062854295212995</v>
       </c>
+      <c r="I48" s="29" t="n">
+        <v>-13.84379592514482</v>
+      </c>
     </row>
     <row r="49" hidden="1" outlineLevel="3">
-      <c r="A49" s="19" t="inlineStr">
+      <c r="A49" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B49" s="20" t="n">
+      <c r="B49" s="31" t="n">
         <v>595840</v>
       </c>
-      <c r="C49" s="21" t="n">
+      <c r="C49" s="32" t="n">
         <v>76</v>
       </c>
-      <c r="D49" s="20" t="n">
-        <v>-576660</v>
-      </c>
-      <c r="E49" s="23" t="n">
+      <c r="D49" s="24" t="n">
+        <v>108505</v>
+      </c>
+      <c r="E49" s="25" t="n">
+        <v>0.1821047921786516</v>
+      </c>
+      <c r="F49" s="26" t="n">
+        <v>-89326</v>
+      </c>
+      <c r="G49" s="34" t="n">
         <v>19180</v>
       </c>
-      <c r="F49" s="24" t="n">
+      <c r="H49" s="35" t="n">
+        <v>0.03218919599946845</v>
+      </c>
+      <c r="I49" s="29" t="n">
+        <v>-14.99155961791831</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" outlineLevel="4">
+      <c r="A50" s="33" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B50" s="31" t="n">
+        <v>595840</v>
+      </c>
+      <c r="C50" s="32" t="n">
+        <v>76</v>
+      </c>
+      <c r="D50" s="24" t="n">
+        <v>108505</v>
+      </c>
+      <c r="E50" s="25" t="n">
+        <v>0.1821047921786516</v>
+      </c>
+      <c r="F50" s="26" t="n">
+        <v>-89326</v>
+      </c>
+      <c r="G50" s="34" t="n">
+        <v>19180</v>
+      </c>
+      <c r="H50" s="35" t="n">
+        <v>0.03218919599946845</v>
+      </c>
+      <c r="I50" s="29" t="n">
+        <v>-14.99155961791831</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" outlineLevel="3">
+      <c r="A51" s="30" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="n">
+        <v>580160</v>
+      </c>
+      <c r="C51" s="32" t="n">
+        <v>74</v>
+      </c>
+      <c r="D51" s="24" t="n">
+        <v>105650</v>
+      </c>
+      <c r="E51" s="25" t="n">
+        <v>0.1821047921786515</v>
+      </c>
+      <c r="F51" s="26" t="n">
+        <v>-86975</v>
+      </c>
+      <c r="G51" s="34" t="n">
+        <v>18675</v>
+      </c>
+      <c r="H51" s="35" t="n">
         <v>0.03218919599946835</v>
       </c>
-    </row>
-    <row r="50" hidden="1" outlineLevel="4">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="I51" s="29" t="n">
+        <v>-14.99155961791832</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" outlineLevel="4">
+      <c r="A52" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B50" s="20" t="n">
-        <v>595840</v>
-      </c>
-      <c r="C50" s="21" t="n">
+      <c r="B52" s="31" t="n">
+        <v>580160</v>
+      </c>
+      <c r="C52" s="32" t="n">
+        <v>74</v>
+      </c>
+      <c r="D52" s="24" t="n">
+        <v>105650</v>
+      </c>
+      <c r="E52" s="25" t="n">
+        <v>0.1821047921786515</v>
+      </c>
+      <c r="F52" s="26" t="n">
+        <v>-86975</v>
+      </c>
+      <c r="G52" s="34" t="n">
+        <v>18675</v>
+      </c>
+      <c r="H52" s="35" t="n">
+        <v>0.03218919599946835</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <v>-14.99155961791832</v>
+      </c>
+    </row>
+    <row r="53" hidden="1" outlineLevel="2">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>MAS_MGT</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="n">
+        <v>1300620</v>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>154</v>
+      </c>
+      <c r="D53" s="24" t="n">
+        <v>313126</v>
+      </c>
+      <c r="E53" s="25" t="n">
+        <v>0.2407513661829102</v>
+      </c>
+      <c r="F53" s="26" t="n">
+        <v>-181002</v>
+      </c>
+      <c r="G53" s="27" t="n">
+        <v>132124</v>
+      </c>
+      <c r="H53" s="28" t="n">
+        <v>0.1015853575078948</v>
+      </c>
+      <c r="I53" s="29" t="n">
+        <v>-13.91660086750154</v>
+      </c>
+    </row>
+    <row r="54" hidden="1" outlineLevel="3">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B54" s="31" t="n">
+        <v>662220</v>
+      </c>
+      <c r="C54" s="32" t="n">
+        <v>78</v>
+      </c>
+      <c r="D54" s="24" t="n">
+        <v>162061</v>
+      </c>
+      <c r="E54" s="25" t="n">
+        <v>0.2447233887727477</v>
+      </c>
+      <c r="F54" s="26" t="n">
+        <v>-91676</v>
+      </c>
+      <c r="G54" s="27" t="n">
+        <v>70384</v>
+      </c>
+      <c r="H54" s="28" t="n">
+        <v>0.1062854295212995</v>
+      </c>
+      <c r="I54" s="29" t="n">
+        <v>-13.84379592514482</v>
+      </c>
+    </row>
+    <row r="55" hidden="1" outlineLevel="4">
+      <c r="A55" s="33" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="n">
+        <v>662220</v>
+      </c>
+      <c r="C55" s="32" t="n">
+        <v>78</v>
+      </c>
+      <c r="D55" s="24" t="n">
+        <v>162061</v>
+      </c>
+      <c r="E55" s="25" t="n">
+        <v>0.2447233887727477</v>
+      </c>
+      <c r="F55" s="26" t="n">
+        <v>-91676</v>
+      </c>
+      <c r="G55" s="27" t="n">
+        <v>70384</v>
+      </c>
+      <c r="H55" s="28" t="n">
+        <v>0.1062854295212995</v>
+      </c>
+      <c r="I55" s="29" t="n">
+        <v>-13.84379592514482</v>
+      </c>
+    </row>
+    <row r="56" hidden="1" outlineLevel="3">
+      <c r="A56" s="30" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B56" s="31" t="n">
+        <v>638400</v>
+      </c>
+      <c r="C56" s="32" t="n">
         <v>76</v>
       </c>
-      <c r="D50" s="20" t="n">
-        <v>-576660</v>
-      </c>
-      <c r="E50" s="23" t="n">
-        <v>19180</v>
-      </c>
-      <c r="F50" s="24" t="n">
-        <v>0.03218919599946835</v>
-      </c>
-    </row>
-    <row r="51" hidden="1" outlineLevel="3">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="n">
-        <v>580160</v>
-      </c>
-      <c r="C51" s="21" t="n">
-        <v>74</v>
-      </c>
-      <c r="D51" s="20" t="n">
-        <v>-561485</v>
-      </c>
-      <c r="E51" s="23" t="n">
-        <v>18675</v>
-      </c>
-      <c r="F51" s="24" t="n">
-        <v>0.03218919599946827</v>
-      </c>
-    </row>
-    <row r="52" hidden="1" outlineLevel="4">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="D56" s="24" t="n">
+        <v>151065</v>
+      </c>
+      <c r="E56" s="25" t="n">
+        <v>0.2366311393667415</v>
+      </c>
+      <c r="F56" s="26" t="n">
+        <v>-89326</v>
+      </c>
+      <c r="G56" s="27" t="n">
+        <v>61740</v>
+      </c>
+      <c r="H56" s="28" t="n">
+        <v>0.09670991626617055</v>
+      </c>
+      <c r="I56" s="29" t="n">
+        <v>-13.99212231005709</v>
+      </c>
+    </row>
+    <row r="57" hidden="1" outlineLevel="4">
+      <c r="A57" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B52" s="20" t="n">
-        <v>580160</v>
-      </c>
-      <c r="C52" s="21" t="n">
-        <v>74</v>
-      </c>
-      <c r="D52" s="20" t="n">
-        <v>-561485</v>
-      </c>
-      <c r="E52" s="23" t="n">
-        <v>18675</v>
-      </c>
-      <c r="F52" s="24" t="n">
-        <v>0.03218919599946827</v>
-      </c>
-    </row>
-    <row r="53" hidden="1" outlineLevel="2">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>MAS_MGT</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n">
-        <v>1300620</v>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>154</v>
-      </c>
-      <c r="D53" s="15" t="n">
-        <v>-1168496</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>132124</v>
-      </c>
-      <c r="F53" s="18" t="n">
-        <v>0.1015853575078949</v>
-      </c>
-    </row>
-    <row r="54" hidden="1" outlineLevel="3">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B54" s="20" t="n">
-        <v>662220</v>
-      </c>
-      <c r="C54" s="21" t="n">
-        <v>78</v>
-      </c>
-      <c r="D54" s="20" t="n">
-        <v>-591836</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>70384</v>
-      </c>
-      <c r="F54" s="18" t="n">
-        <v>0.1062854295212995</v>
-      </c>
-    </row>
-    <row r="55" hidden="1" outlineLevel="4">
-      <c r="A55" s="22" t="inlineStr">
-        <is>
-          <t>Alternance</t>
-        </is>
-      </c>
-      <c r="B55" s="20" t="n">
-        <v>662220</v>
-      </c>
-      <c r="C55" s="21" t="n">
-        <v>78</v>
-      </c>
-      <c r="D55" s="20" t="n">
-        <v>-591836</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>70384</v>
-      </c>
-      <c r="F55" s="18" t="n">
-        <v>0.1062854295212995</v>
-      </c>
-    </row>
-    <row r="56" hidden="1" outlineLevel="3">
-      <c r="A56" s="19" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="B56" s="20" t="n">
+      <c r="B57" s="31" t="n">
         <v>638400</v>
       </c>
-      <c r="C56" s="21" t="n">
+      <c r="C57" s="32" t="n">
         <v>76</v>
       </c>
-      <c r="D56" s="20" t="n">
-        <v>-576660</v>
-      </c>
-      <c r="E56" s="17" t="n">
+      <c r="D57" s="24" t="n">
+        <v>151065</v>
+      </c>
+      <c r="E57" s="25" t="n">
+        <v>0.2366311393667415</v>
+      </c>
+      <c r="F57" s="26" t="n">
+        <v>-89326</v>
+      </c>
+      <c r="G57" s="27" t="n">
         <v>61740</v>
       </c>
-      <c r="F56" s="18" t="n">
-        <v>0.09670991626617047</v>
-      </c>
-    </row>
-    <row r="57" hidden="1" outlineLevel="4">
-      <c r="A57" s="22" t="inlineStr">
-        <is>
-          <t>Alternance</t>
-        </is>
-      </c>
-      <c r="B57" s="20" t="n">
-        <v>638400</v>
-      </c>
-      <c r="C57" s="21" t="n">
-        <v>76</v>
-      </c>
-      <c r="D57" s="20" t="n">
-        <v>-576660</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>61740</v>
-      </c>
-      <c r="F57" s="18" t="n">
-        <v>0.09670991626617047</v>
+      <c r="H57" s="28" t="n">
+        <v>0.09670991626617055</v>
+      </c>
+      <c r="I57" s="29" t="n">
+        <v>-13.99212231005709</v>
       </c>
     </row>
     <row r="58">
@@ -1845,872 +2409,1232 @@
       <c r="C58" s="7" t="n">
         <v>829</v>
       </c>
-      <c r="D58" s="6" t="n">
-        <v>-5290478</v>
-      </c>
-      <c r="E58" s="6" t="n">
+      <c r="D58" s="8" t="n">
+        <v>1976427</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>0.3140899953119164</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>-974355</v>
+      </c>
+      <c r="G58" s="6" t="n">
         <v>1002072</v>
       </c>
-      <c r="F58" s="8" t="n">
-        <v>0.1592472957412914</v>
+      <c r="H58" s="11" t="n">
+        <v>0.1592472957412916</v>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>-15.48426995706249</v>
       </c>
     </row>
     <row r="59" hidden="1" outlineLevel="1">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
       </c>
-      <c r="B59" s="10" t="n">
+      <c r="B59" s="14" t="n">
         <v>1755850</v>
       </c>
-      <c r="C59" s="11" t="n">
+      <c r="C59" s="15" t="n">
         <v>244</v>
       </c>
-      <c r="D59" s="10" t="n">
-        <v>-1286975</v>
-      </c>
-      <c r="E59" s="12" t="n">
+      <c r="D59" s="14" t="n">
+        <v>755658</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>0.4303659196400604</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>-286783</v>
+      </c>
+      <c r="G59" s="18" t="n">
         <v>468875</v>
       </c>
-      <c r="F59" s="13" t="n">
-        <v>0.2670361711610159</v>
+      <c r="H59" s="19" t="n">
+        <v>0.267036171161016</v>
+      </c>
+      <c r="I59" s="20" t="n">
+        <v>-16.33297484790444</v>
       </c>
     </row>
     <row r="60" hidden="1" outlineLevel="2">
-      <c r="A60" s="14" t="inlineStr">
+      <c r="A60" s="21" t="inlineStr">
         <is>
           <t>BAC_COM</t>
         </is>
       </c>
-      <c r="B60" s="15" t="n">
+      <c r="B60" s="22" t="n">
         <v>1023700</v>
       </c>
-      <c r="C60" s="16" t="n">
+      <c r="C60" s="23" t="n">
         <v>145</v>
       </c>
-      <c r="D60" s="15" t="n">
-        <v>-764800</v>
-      </c>
-      <c r="E60" s="17" t="n">
+      <c r="D60" s="24" t="n">
+        <v>429324</v>
+      </c>
+      <c r="E60" s="25" t="n">
+        <v>0.4193842009938235</v>
+      </c>
+      <c r="F60" s="26" t="n">
+        <v>-170424</v>
+      </c>
+      <c r="G60" s="27" t="n">
         <v>258900</v>
       </c>
-      <c r="F60" s="18" t="n">
+      <c r="H60" s="28" t="n">
         <v>0.2529056919223227</v>
       </c>
+      <c r="I60" s="29" t="n">
+        <v>-16.64785090715008</v>
+      </c>
     </row>
     <row r="61" hidden="1" outlineLevel="3">
-      <c r="A61" s="19" t="inlineStr">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n">
+      <c r="B61" s="31" t="n">
         <v>372000</v>
       </c>
-      <c r="C61" s="21" t="n">
+      <c r="C61" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="D61" s="20" t="n">
-        <v>-263724</v>
-      </c>
-      <c r="E61" s="17" t="n">
+      <c r="D61" s="24" t="n">
+        <v>167043</v>
+      </c>
+      <c r="E61" s="25" t="n">
+        <v>0.4490393090075798</v>
+      </c>
+      <c r="F61" s="26" t="n">
+        <v>-58767</v>
+      </c>
+      <c r="G61" s="27" t="n">
         <v>108276</v>
       </c>
-      <c r="F61" s="18" t="n">
+      <c r="H61" s="28" t="n">
         <v>0.2910637345391932</v>
       </c>
+      <c r="I61" s="29" t="n">
+        <v>-15.79755744683866</v>
+      </c>
     </row>
     <row r="62" hidden="1" outlineLevel="4">
-      <c r="A62" s="22" t="inlineStr">
+      <c r="A62" s="33" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="B62" s="20" t="n">
+      <c r="B62" s="31" t="n">
         <v>372000</v>
       </c>
-      <c r="C62" s="21" t="n">
+      <c r="C62" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="D62" s="20" t="n">
-        <v>-263724</v>
-      </c>
-      <c r="E62" s="17" t="n">
+      <c r="D62" s="24" t="n">
+        <v>167043</v>
+      </c>
+      <c r="E62" s="25" t="n">
+        <v>0.4490393090075798</v>
+      </c>
+      <c r="F62" s="26" t="n">
+        <v>-58767</v>
+      </c>
+      <c r="G62" s="27" t="n">
         <v>108276</v>
       </c>
-      <c r="F62" s="18" t="n">
+      <c r="H62" s="28" t="n">
         <v>0.2910637345391932</v>
       </c>
+      <c r="I62" s="29" t="n">
+        <v>-15.79755744683866</v>
+      </c>
     </row>
     <row r="63" hidden="1" outlineLevel="3">
-      <c r="A63" s="19" t="inlineStr">
+      <c r="A63" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B63" s="20" t="n">
+      <c r="B63" s="31" t="n">
         <v>329280</v>
       </c>
-      <c r="C63" s="21" t="n">
+      <c r="C63" s="32" t="n">
         <v>48</v>
       </c>
-      <c r="D63" s="20" t="n">
-        <v>-253175</v>
-      </c>
-      <c r="E63" s="17" t="n">
+      <c r="D63" s="24" t="n">
+        <v>132521</v>
+      </c>
+      <c r="E63" s="25" t="n">
+        <v>0.4024566266787746</v>
+      </c>
+      <c r="F63" s="26" t="n">
+        <v>-56416</v>
+      </c>
+      <c r="G63" s="27" t="n">
         <v>76105</v>
       </c>
-      <c r="F63" s="18" t="n">
+      <c r="H63" s="28" t="n">
         <v>0.2311245167597082</v>
       </c>
+      <c r="I63" s="29" t="n">
+        <v>-17.13321099190664</v>
+      </c>
     </row>
     <row r="64" hidden="1" outlineLevel="4">
-      <c r="A64" s="22" t="inlineStr">
+      <c r="A64" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B64" s="20" t="n">
+      <c r="B64" s="31" t="n">
         <v>329280</v>
       </c>
-      <c r="C64" s="21" t="n">
+      <c r="C64" s="32" t="n">
         <v>48</v>
       </c>
-      <c r="D64" s="20" t="n">
-        <v>-253175</v>
-      </c>
-      <c r="E64" s="17" t="n">
+      <c r="D64" s="24" t="n">
+        <v>132521</v>
+      </c>
+      <c r="E64" s="25" t="n">
+        <v>0.4024566266787746</v>
+      </c>
+      <c r="F64" s="26" t="n">
+        <v>-56416</v>
+      </c>
+      <c r="G64" s="27" t="n">
         <v>76105</v>
       </c>
-      <c r="F64" s="18" t="n">
+      <c r="H64" s="28" t="n">
         <v>0.2311245167597082</v>
       </c>
+      <c r="I64" s="29" t="n">
+        <v>-17.13321099190664</v>
+      </c>
     </row>
     <row r="65" hidden="1" outlineLevel="3">
-      <c r="A65" s="19" t="inlineStr">
+      <c r="A65" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B65" s="20" t="n">
+      <c r="B65" s="31" t="n">
         <v>322420</v>
       </c>
-      <c r="C65" s="21" t="n">
+      <c r="C65" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="D65" s="20" t="n">
-        <v>-247901</v>
-      </c>
-      <c r="E65" s="17" t="n">
+      <c r="D65" s="24" t="n">
+        <v>129760</v>
+      </c>
+      <c r="E65" s="25" t="n">
+        <v>0.4024566266787746</v>
+      </c>
+      <c r="F65" s="26" t="n">
+        <v>-55241</v>
+      </c>
+      <c r="G65" s="27" t="n">
         <v>74519</v>
       </c>
-      <c r="F65" s="18" t="n">
+      <c r="H65" s="28" t="n">
         <v>0.2311245167597081</v>
       </c>
+      <c r="I65" s="29" t="n">
+        <v>-17.13321099190665</v>
+      </c>
     </row>
     <row r="66" hidden="1" outlineLevel="4">
-      <c r="A66" s="22" t="inlineStr">
+      <c r="A66" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B66" s="20" t="n">
+      <c r="B66" s="31" t="n">
         <v>322420</v>
       </c>
-      <c r="C66" s="21" t="n">
+      <c r="C66" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="D66" s="20" t="n">
-        <v>-247901</v>
-      </c>
-      <c r="E66" s="17" t="n">
+      <c r="D66" s="24" t="n">
+        <v>129760</v>
+      </c>
+      <c r="E66" s="25" t="n">
+        <v>0.4024566266787746</v>
+      </c>
+      <c r="F66" s="26" t="n">
+        <v>-55241</v>
+      </c>
+      <c r="G66" s="27" t="n">
         <v>74519</v>
       </c>
-      <c r="F66" s="18" t="n">
+      <c r="H66" s="28" t="n">
         <v>0.2311245167597081</v>
       </c>
+      <c r="I66" s="29" t="n">
+        <v>-17.13321099190665</v>
+      </c>
     </row>
     <row r="67" hidden="1" outlineLevel="2">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>MAS_COM</t>
         </is>
       </c>
-      <c r="B67" s="15" t="n">
+      <c r="B67" s="22" t="n">
         <v>732150</v>
       </c>
-      <c r="C67" s="16" t="n">
+      <c r="C67" s="23" t="n">
         <v>99</v>
       </c>
-      <c r="D67" s="15" t="n">
-        <v>-522174</v>
-      </c>
-      <c r="E67" s="17" t="n">
+      <c r="D67" s="24" t="n">
+        <v>326334</v>
+      </c>
+      <c r="E67" s="25" t="n">
+        <v>0.4457206766955173</v>
+      </c>
+      <c r="F67" s="26" t="n">
+        <v>-116358</v>
+      </c>
+      <c r="G67" s="27" t="n">
         <v>209976</v>
       </c>
-      <c r="F67" s="18" t="n">
-        <v>0.2867935591233875</v>
+      <c r="H67" s="28" t="n">
+        <v>0.2867935591233876</v>
+      </c>
+      <c r="I67" s="29" t="n">
+        <v>-15.89271175721297</v>
       </c>
     </row>
     <row r="68" hidden="1" outlineLevel="3">
-      <c r="A68" s="19" t="inlineStr">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B68" s="20" t="n">
+      <c r="B68" s="31" t="n">
         <v>372000</v>
       </c>
-      <c r="C68" s="21" t="n">
+      <c r="C68" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="D68" s="20" t="n">
-        <v>-263724</v>
-      </c>
-      <c r="E68" s="17" t="n">
+      <c r="D68" s="24" t="n">
+        <v>167043</v>
+      </c>
+      <c r="E68" s="25" t="n">
+        <v>0.4490393090075798</v>
+      </c>
+      <c r="F68" s="26" t="n">
+        <v>-58767</v>
+      </c>
+      <c r="G68" s="27" t="n">
         <v>108276</v>
       </c>
-      <c r="F68" s="18" t="n">
+      <c r="H68" s="28" t="n">
         <v>0.2910637345391932</v>
       </c>
+      <c r="I68" s="29" t="n">
+        <v>-15.79755744683866</v>
+      </c>
     </row>
     <row r="69" hidden="1" outlineLevel="4">
-      <c r="A69" s="22" t="inlineStr">
+      <c r="A69" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B69" s="20" t="n">
+      <c r="B69" s="31" t="n">
         <v>372000</v>
       </c>
-      <c r="C69" s="21" t="n">
+      <c r="C69" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="D69" s="20" t="n">
-        <v>-263724</v>
-      </c>
-      <c r="E69" s="17" t="n">
+      <c r="D69" s="24" t="n">
+        <v>167043</v>
+      </c>
+      <c r="E69" s="25" t="n">
+        <v>0.4490393090075798</v>
+      </c>
+      <c r="F69" s="26" t="n">
+        <v>-58767</v>
+      </c>
+      <c r="G69" s="27" t="n">
         <v>108276</v>
       </c>
-      <c r="F69" s="18" t="n">
+      <c r="H69" s="28" t="n">
         <v>0.2910637345391932</v>
       </c>
+      <c r="I69" s="29" t="n">
+        <v>-15.79755744683866</v>
+      </c>
     </row>
     <row r="70" hidden="1" outlineLevel="3">
-      <c r="A70" s="19" t="inlineStr">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B70" s="20" t="n">
+      <c r="B70" s="31" t="n">
         <v>360150</v>
       </c>
-      <c r="C70" s="21" t="n">
+      <c r="C70" s="32" t="n">
         <v>49</v>
       </c>
-      <c r="D70" s="20" t="n">
-        <v>-258450</v>
-      </c>
-      <c r="E70" s="17" t="n">
+      <c r="D70" s="24" t="n">
+        <v>159292</v>
+      </c>
+      <c r="E70" s="25" t="n">
+        <v>0.4422928515668562</v>
+      </c>
+      <c r="F70" s="26" t="n">
+        <v>-57592</v>
+      </c>
+      <c r="G70" s="27" t="n">
         <v>101700</v>
       </c>
-      <c r="F70" s="18" t="n">
+      <c r="H70" s="28" t="n">
         <v>0.2823828823090608</v>
       </c>
+      <c r="I70" s="29" t="n">
+        <v>-15.99099692577954</v>
+      </c>
     </row>
     <row r="71" hidden="1" outlineLevel="4">
-      <c r="A71" s="22" t="inlineStr">
+      <c r="A71" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B71" s="20" t="n">
+      <c r="B71" s="31" t="n">
         <v>360150</v>
       </c>
-      <c r="C71" s="21" t="n">
+      <c r="C71" s="32" t="n">
         <v>49</v>
       </c>
-      <c r="D71" s="20" t="n">
-        <v>-258450</v>
-      </c>
-      <c r="E71" s="17" t="n">
+      <c r="D71" s="24" t="n">
+        <v>159292</v>
+      </c>
+      <c r="E71" s="25" t="n">
+        <v>0.4422928515668562</v>
+      </c>
+      <c r="F71" s="26" t="n">
+        <v>-57592</v>
+      </c>
+      <c r="G71" s="27" t="n">
         <v>101700</v>
       </c>
-      <c r="F71" s="18" t="n">
+      <c r="H71" s="28" t="n">
         <v>0.2823828823090608</v>
       </c>
+      <c r="I71" s="29" t="n">
+        <v>-15.99099692577954</v>
+      </c>
     </row>
     <row r="72" hidden="1" outlineLevel="1">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="B72" s="10" t="n">
+      <c r="B72" s="14" t="n">
         <v>2908720</v>
       </c>
-      <c r="C72" s="11" t="n">
+      <c r="C72" s="15" t="n">
         <v>354</v>
       </c>
-      <c r="D72" s="10" t="n">
-        <v>-2775096</v>
-      </c>
-      <c r="E72" s="25" t="n">
+      <c r="D72" s="14" t="n">
+        <v>549694</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>0.1889814076294728</v>
+      </c>
+      <c r="F72" s="17" t="n">
+        <v>-416070</v>
+      </c>
+      <c r="G72" s="36" t="n">
         <v>133624</v>
       </c>
-      <c r="F72" s="26" t="n">
-        <v>0.04593919352434804</v>
+      <c r="H72" s="37" t="n">
+        <v>0.04593919352434826</v>
+      </c>
+      <c r="I72" s="20" t="n">
+        <v>-14.30422141051245</v>
       </c>
     </row>
     <row r="73" hidden="1" outlineLevel="2">
-      <c r="A73" s="14" t="inlineStr">
+      <c r="A73" s="21" t="inlineStr">
         <is>
           <t>BAC_COM</t>
         </is>
       </c>
-      <c r="B73" s="15" t="n">
+      <c r="B73" s="22" t="n">
         <v>1701040</v>
       </c>
-      <c r="C73" s="16" t="n">
+      <c r="C73" s="23" t="n">
         <v>211</v>
       </c>
-      <c r="D73" s="15" t="n">
-        <v>-1654082</v>
-      </c>
-      <c r="E73" s="23" t="n">
+      <c r="D73" s="24" t="n">
+        <v>294954</v>
+      </c>
+      <c r="E73" s="25" t="n">
+        <v>0.1733962054719067</v>
+      </c>
+      <c r="F73" s="26" t="n">
+        <v>-247996</v>
+      </c>
+      <c r="G73" s="34" t="n">
         <v>46958</v>
       </c>
-      <c r="F73" s="24" t="n">
-        <v>0.0276051742066501</v>
+      <c r="H73" s="35" t="n">
+        <v>0.02760517420665021</v>
+      </c>
+      <c r="I73" s="29" t="n">
+        <v>-14.57910312652565</v>
       </c>
     </row>
     <row r="74" hidden="1" outlineLevel="3">
-      <c r="A74" s="19" t="inlineStr">
+      <c r="A74" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B74" s="20" t="n">
+      <c r="B74" s="31" t="n">
         <v>611280</v>
       </c>
-      <c r="C74" s="21" t="n">
+      <c r="C74" s="32" t="n">
         <v>72</v>
       </c>
-      <c r="D74" s="20" t="n">
-        <v>-564426</v>
-      </c>
-      <c r="E74" s="17" t="n">
+      <c r="D74" s="24" t="n">
+        <v>131478</v>
+      </c>
+      <c r="E74" s="25" t="n">
+        <v>0.2150865424926633</v>
+      </c>
+      <c r="F74" s="26" t="n">
+        <v>-84624</v>
+      </c>
+      <c r="G74" s="27" t="n">
         <v>46854</v>
       </c>
-      <c r="F74" s="18" t="n">
-        <v>0.07664858324121494</v>
+      <c r="H74" s="28" t="n">
+        <v>0.07664858324121501</v>
+      </c>
+      <c r="I74" s="29" t="n">
+        <v>-13.84379592514483</v>
       </c>
     </row>
     <row r="75" hidden="1" outlineLevel="4">
-      <c r="A75" s="22" t="inlineStr">
+      <c r="A75" s="33" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="B75" s="20" t="n">
+      <c r="B75" s="31" t="n">
         <v>611280</v>
       </c>
-      <c r="C75" s="21" t="n">
+      <c r="C75" s="32" t="n">
         <v>72</v>
       </c>
-      <c r="D75" s="20" t="n">
-        <v>-564426</v>
-      </c>
-      <c r="E75" s="17" t="n">
+      <c r="D75" s="24" t="n">
+        <v>131478</v>
+      </c>
+      <c r="E75" s="25" t="n">
+        <v>0.2150865424926633</v>
+      </c>
+      <c r="F75" s="26" t="n">
+        <v>-84624</v>
+      </c>
+      <c r="G75" s="27" t="n">
         <v>46854</v>
       </c>
-      <c r="F75" s="18" t="n">
-        <v>0.07664858324121494</v>
+      <c r="H75" s="28" t="n">
+        <v>0.07664858324121501</v>
+      </c>
+      <c r="I75" s="29" t="n">
+        <v>-13.84379592514483</v>
       </c>
     </row>
     <row r="76" hidden="1" outlineLevel="3">
-      <c r="A76" s="19" t="inlineStr">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B76" s="20" t="n">
+      <c r="B76" s="31" t="n">
         <v>548800</v>
       </c>
-      <c r="C76" s="21" t="n">
+      <c r="C76" s="32" t="n">
         <v>70</v>
       </c>
-      <c r="D76" s="20" t="n">
-        <v>-548748</v>
-      </c>
-      <c r="E76" s="23" t="n">
+      <c r="D76" s="24" t="n">
+        <v>82326</v>
+      </c>
+      <c r="E76" s="25" t="n">
+        <v>0.1500108094085091</v>
+      </c>
+      <c r="F76" s="26" t="n">
+        <v>-82274</v>
+      </c>
+      <c r="G76" s="34" t="n">
         <v>52</v>
       </c>
-      <c r="F76" s="24" t="n">
-        <v>9.521322932594785e-05</v>
+      <c r="H76" s="35" t="n">
+        <v>9.52132293260009e-05</v>
+      </c>
+      <c r="I76" s="29" t="n">
+        <v>-14.99155961791831</v>
       </c>
     </row>
     <row r="77" hidden="1" outlineLevel="4">
-      <c r="A77" s="22" t="inlineStr">
+      <c r="A77" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B77" s="20" t="n">
+      <c r="B77" s="31" t="n">
         <v>548800</v>
       </c>
-      <c r="C77" s="21" t="n">
+      <c r="C77" s="32" t="n">
         <v>70</v>
       </c>
-      <c r="D77" s="20" t="n">
-        <v>-548748</v>
-      </c>
-      <c r="E77" s="23" t="n">
+      <c r="D77" s="24" t="n">
+        <v>82326</v>
+      </c>
+      <c r="E77" s="25" t="n">
+        <v>0.1500108094085091</v>
+      </c>
+      <c r="F77" s="26" t="n">
+        <v>-82274</v>
+      </c>
+      <c r="G77" s="34" t="n">
         <v>52</v>
       </c>
-      <c r="F77" s="24" t="n">
-        <v>9.521322932594785e-05</v>
+      <c r="H77" s="35" t="n">
+        <v>9.52132293260009e-05</v>
+      </c>
+      <c r="I77" s="29" t="n">
+        <v>-14.99155961791831</v>
       </c>
     </row>
     <row r="78" hidden="1" outlineLevel="3">
-      <c r="A78" s="19" t="inlineStr">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B78" s="20" t="n">
+      <c r="B78" s="31" t="n">
         <v>540960</v>
       </c>
-      <c r="C78" s="21" t="n">
+      <c r="C78" s="32" t="n">
         <v>69</v>
       </c>
-      <c r="D78" s="20" t="n">
-        <v>-540908</v>
-      </c>
-      <c r="E78" s="23" t="n">
+      <c r="D78" s="24" t="n">
+        <v>81150</v>
+      </c>
+      <c r="E78" s="25" t="n">
+        <v>0.1500108094085092</v>
+      </c>
+      <c r="F78" s="26" t="n">
+        <v>-81098</v>
+      </c>
+      <c r="G78" s="34" t="n">
         <v>52</v>
       </c>
-      <c r="F78" s="24" t="n">
-        <v>9.521322932609235e-05</v>
+      <c r="H78" s="35" t="n">
+        <v>9.521322932603854e-05</v>
+      </c>
+      <c r="I78" s="29" t="n">
+        <v>-14.99155961791831</v>
       </c>
     </row>
     <row r="79" hidden="1" outlineLevel="4">
-      <c r="A79" s="22" t="inlineStr">
+      <c r="A79" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B79" s="20" t="n">
+      <c r="B79" s="31" t="n">
         <v>540960</v>
       </c>
-      <c r="C79" s="21" t="n">
+      <c r="C79" s="32" t="n">
         <v>69</v>
       </c>
-      <c r="D79" s="20" t="n">
-        <v>-540908</v>
-      </c>
-      <c r="E79" s="23" t="n">
+      <c r="D79" s="24" t="n">
+        <v>81150</v>
+      </c>
+      <c r="E79" s="25" t="n">
+        <v>0.1500108094085092</v>
+      </c>
+      <c r="F79" s="26" t="n">
+        <v>-81098</v>
+      </c>
+      <c r="G79" s="34" t="n">
         <v>52</v>
       </c>
-      <c r="F79" s="24" t="n">
-        <v>9.521322932609235e-05</v>
+      <c r="H79" s="35" t="n">
+        <v>9.521322932603854e-05</v>
+      </c>
+      <c r="I79" s="29" t="n">
+        <v>-14.99155961791831</v>
       </c>
     </row>
     <row r="80" hidden="1" outlineLevel="2">
-      <c r="A80" s="14" t="inlineStr">
+      <c r="A80" s="21" t="inlineStr">
         <is>
           <t>MAS_COM</t>
         </is>
       </c>
-      <c r="B80" s="15" t="n">
+      <c r="B80" s="22" t="n">
         <v>1207680</v>
       </c>
-      <c r="C80" s="16" t="n">
+      <c r="C80" s="23" t="n">
         <v>143</v>
       </c>
-      <c r="D80" s="15" t="n">
-        <v>-1121013</v>
-      </c>
-      <c r="E80" s="17" t="n">
+      <c r="D80" s="24" t="n">
+        <v>254740</v>
+      </c>
+      <c r="E80" s="25" t="n">
+        <v>0.2109334580717308</v>
+      </c>
+      <c r="F80" s="26" t="n">
+        <v>-168073</v>
+      </c>
+      <c r="G80" s="27" t="n">
         <v>86667</v>
       </c>
-      <c r="F80" s="18" t="n">
-        <v>0.07176300464995843</v>
+      <c r="H80" s="28" t="n">
+        <v>0.07176300464995859</v>
+      </c>
+      <c r="I80" s="29" t="n">
+        <v>-13.91704534217721</v>
       </c>
     </row>
     <row r="81" hidden="1" outlineLevel="3">
-      <c r="A81" s="19" t="inlineStr">
+      <c r="A81" s="30" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B81" s="20" t="n">
+      <c r="B81" s="31" t="n">
         <v>611280</v>
       </c>
-      <c r="C81" s="21" t="n">
+      <c r="C81" s="32" t="n">
         <v>72</v>
       </c>
-      <c r="D81" s="20" t="n">
-        <v>-564426</v>
-      </c>
-      <c r="E81" s="17" t="n">
+      <c r="D81" s="24" t="n">
+        <v>131478</v>
+      </c>
+      <c r="E81" s="25" t="n">
+        <v>0.2150865424926633</v>
+      </c>
+      <c r="F81" s="26" t="n">
+        <v>-84624</v>
+      </c>
+      <c r="G81" s="27" t="n">
         <v>46854</v>
       </c>
-      <c r="F81" s="18" t="n">
-        <v>0.07664858324121494</v>
+      <c r="H81" s="28" t="n">
+        <v>0.07664858324121501</v>
+      </c>
+      <c r="I81" s="29" t="n">
+        <v>-13.84379592514483</v>
       </c>
     </row>
     <row r="82" hidden="1" outlineLevel="4">
-      <c r="A82" s="22" t="inlineStr">
+      <c r="A82" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B82" s="20" t="n">
+      <c r="B82" s="31" t="n">
         <v>611280</v>
       </c>
-      <c r="C82" s="21" t="n">
+      <c r="C82" s="32" t="n">
         <v>72</v>
       </c>
-      <c r="D82" s="20" t="n">
-        <v>-564426</v>
-      </c>
-      <c r="E82" s="17" t="n">
+      <c r="D82" s="24" t="n">
+        <v>131478</v>
+      </c>
+      <c r="E82" s="25" t="n">
+        <v>0.2150865424926633</v>
+      </c>
+      <c r="F82" s="26" t="n">
+        <v>-84624</v>
+      </c>
+      <c r="G82" s="27" t="n">
         <v>46854</v>
       </c>
-      <c r="F82" s="18" t="n">
-        <v>0.07664858324121494</v>
+      <c r="H82" s="28" t="n">
+        <v>0.07664858324121501</v>
+      </c>
+      <c r="I82" s="29" t="n">
+        <v>-13.84379592514483</v>
       </c>
     </row>
     <row r="83" hidden="1" outlineLevel="3">
-      <c r="A83" s="19" t="inlineStr">
+      <c r="A83" s="30" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B83" s="20" t="n">
+      <c r="B83" s="31" t="n">
         <v>596400</v>
       </c>
-      <c r="C83" s="21" t="n">
+      <c r="C83" s="32" t="n">
         <v>71</v>
       </c>
-      <c r="D83" s="20" t="n">
-        <v>-556587</v>
-      </c>
-      <c r="E83" s="17" t="n">
+      <c r="D83" s="24" t="n">
+        <v>123262</v>
+      </c>
+      <c r="E83" s="25" t="n">
+        <v>0.2066767554479418</v>
+      </c>
+      <c r="F83" s="26" t="n">
+        <v>-83449</v>
+      </c>
+      <c r="G83" s="27" t="n">
         <v>39813</v>
       </c>
-      <c r="F83" s="18" t="n">
-        <v>0.06675553234737094</v>
+      <c r="H83" s="28" t="n">
+        <v>0.06675553234737093</v>
+      </c>
+      <c r="I83" s="29" t="n">
+        <v>-13.99212231005709</v>
       </c>
     </row>
     <row r="84" hidden="1" outlineLevel="4">
-      <c r="A84" s="22" t="inlineStr">
+      <c r="A84" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B84" s="20" t="n">
+      <c r="B84" s="31" t="n">
         <v>596400</v>
       </c>
-      <c r="C84" s="21" t="n">
+      <c r="C84" s="32" t="n">
         <v>71</v>
       </c>
-      <c r="D84" s="20" t="n">
-        <v>-556587</v>
-      </c>
-      <c r="E84" s="17" t="n">
+      <c r="D84" s="24" t="n">
+        <v>123262</v>
+      </c>
+      <c r="E84" s="25" t="n">
+        <v>0.2066767554479418</v>
+      </c>
+      <c r="F84" s="26" t="n">
+        <v>-83449</v>
+      </c>
+      <c r="G84" s="27" t="n">
         <v>39813</v>
       </c>
-      <c r="F84" s="18" t="n">
-        <v>0.06675553234737094</v>
+      <c r="H84" s="28" t="n">
+        <v>0.06675553234737093</v>
+      </c>
+      <c r="I84" s="29" t="n">
+        <v>-13.99212231005709</v>
       </c>
     </row>
     <row r="85" hidden="1" outlineLevel="1">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="B85" s="10" t="n">
+      <c r="B85" s="14" t="n">
         <v>1627980</v>
       </c>
-      <c r="C85" s="11" t="n">
+      <c r="C85" s="15" t="n">
         <v>231</v>
       </c>
-      <c r="D85" s="10" t="n">
-        <v>-1228408</v>
-      </c>
-      <c r="E85" s="12" t="n">
+      <c r="D85" s="14" t="n">
+        <v>671075</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>0.4122132950036241</v>
+      </c>
+      <c r="F85" s="17" t="n">
+        <v>-271503</v>
+      </c>
+      <c r="G85" s="18" t="n">
         <v>399572</v>
       </c>
-      <c r="F85" s="13" t="n">
+      <c r="H85" s="19" t="n">
         <v>0.2454402748778561</v>
       </c>
+      <c r="I85" s="20" t="n">
+        <v>-16.67730201257681</v>
+      </c>
     </row>
     <row r="86" hidden="1" outlineLevel="2">
-      <c r="A86" s="14" t="inlineStr">
+      <c r="A86" s="21" t="inlineStr">
         <is>
           <t>BAC_COM</t>
         </is>
       </c>
-      <c r="B86" s="15" t="n">
+      <c r="B86" s="22" t="n">
         <v>954150</v>
       </c>
-      <c r="C86" s="16" t="n">
+      <c r="C86" s="23" t="n">
         <v>138</v>
       </c>
-      <c r="D86" s="15" t="n">
-        <v>-733854</v>
-      </c>
-      <c r="E86" s="17" t="n">
+      <c r="D86" s="24" t="n">
+        <v>382492</v>
+      </c>
+      <c r="E86" s="25" t="n">
+        <v>0.400872470295517</v>
+      </c>
+      <c r="F86" s="26" t="n">
+        <v>-162197</v>
+      </c>
+      <c r="G86" s="27" t="n">
         <v>220296</v>
       </c>
-      <c r="F86" s="18" t="n">
-        <v>0.2308817122195521</v>
+      <c r="H86" s="28" t="n">
+        <v>0.2308817122195522</v>
+      </c>
+      <c r="I86" s="29" t="n">
+        <v>-16.99907580759648</v>
       </c>
     </row>
     <row r="87" hidden="1" outlineLevel="3">
-      <c r="A87" s="19" t="inlineStr">
+      <c r="A87" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B87" s="20" t="n">
+      <c r="B87" s="31" t="n">
         <v>342630</v>
       </c>
-      <c r="C87" s="21" t="n">
+      <c r="C87" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="D87" s="20" t="n">
-        <v>-249936</v>
-      </c>
-      <c r="E87" s="17" t="n">
+      <c r="D87" s="24" t="n">
+        <v>147935</v>
+      </c>
+      <c r="E87" s="25" t="n">
+        <v>0.4317632527509071</v>
+      </c>
+      <c r="F87" s="26" t="n">
+        <v>-55241</v>
+      </c>
+      <c r="G87" s="27" t="n">
         <v>92694</v>
       </c>
-      <c r="F87" s="18" t="n">
+      <c r="H87" s="28" t="n">
         <v>0.2705371520588912</v>
       </c>
+      <c r="I87" s="29" t="n">
+        <v>-16.12261006920159</v>
+      </c>
     </row>
     <row r="88" hidden="1" outlineLevel="4">
-      <c r="A88" s="22" t="inlineStr">
+      <c r="A88" s="33" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="B88" s="20" t="n">
+      <c r="B88" s="31" t="n">
         <v>342630</v>
       </c>
-      <c r="C88" s="21" t="n">
+      <c r="C88" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="D88" s="20" t="n">
-        <v>-249936</v>
-      </c>
-      <c r="E88" s="17" t="n">
+      <c r="D88" s="24" t="n">
+        <v>147935</v>
+      </c>
+      <c r="E88" s="25" t="n">
+        <v>0.4317632527509071</v>
+      </c>
+      <c r="F88" s="26" t="n">
+        <v>-55241</v>
+      </c>
+      <c r="G88" s="27" t="n">
         <v>92694</v>
       </c>
-      <c r="F88" s="18" t="n">
+      <c r="H88" s="28" t="n">
         <v>0.2705371520588912</v>
       </c>
+      <c r="I88" s="29" t="n">
+        <v>-16.12261006920159</v>
+      </c>
     </row>
     <row r="89" hidden="1" outlineLevel="3">
-      <c r="A89" s="19" t="inlineStr">
+      <c r="A89" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B89" s="20" t="n">
+      <c r="B89" s="31" t="n">
         <v>309120</v>
       </c>
-      <c r="C89" s="21" t="n">
+      <c r="C89" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D89" s="20" t="n">
-        <v>-244618</v>
-      </c>
-      <c r="E89" s="17" t="n">
+      <c r="D89" s="24" t="n">
+        <v>118567</v>
+      </c>
+      <c r="E89" s="25" t="n">
+        <v>0.3835646000824572</v>
+      </c>
+      <c r="F89" s="26" t="n">
+        <v>-54066</v>
+      </c>
+      <c r="G89" s="27" t="n">
         <v>64502</v>
       </c>
-      <c r="F89" s="18" t="n">
+      <c r="H89" s="28" t="n">
         <v>0.2086630712067436</v>
       </c>
+      <c r="I89" s="29" t="n">
+        <v>-17.49015288757136</v>
+      </c>
     </row>
     <row r="90" hidden="1" outlineLevel="4">
-      <c r="A90" s="22" t="inlineStr">
+      <c r="A90" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B90" s="20" t="n">
+      <c r="B90" s="31" t="n">
         <v>309120</v>
       </c>
-      <c r="C90" s="21" t="n">
+      <c r="C90" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D90" s="20" t="n">
-        <v>-244618</v>
-      </c>
-      <c r="E90" s="17" t="n">
+      <c r="D90" s="24" t="n">
+        <v>118567</v>
+      </c>
+      <c r="E90" s="25" t="n">
+        <v>0.3835646000824572</v>
+      </c>
+      <c r="F90" s="26" t="n">
+        <v>-54066</v>
+      </c>
+      <c r="G90" s="27" t="n">
         <v>64502</v>
       </c>
-      <c r="F90" s="18" t="n">
+      <c r="H90" s="28" t="n">
         <v>0.2086630712067436</v>
       </c>
+      <c r="I90" s="29" t="n">
+        <v>-17.49015288757136</v>
+      </c>
     </row>
     <row r="91" hidden="1" outlineLevel="3">
-      <c r="A91" s="19" t="inlineStr">
+      <c r="A91" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B91" s="20" t="n">
+      <c r="B91" s="31" t="n">
         <v>302400</v>
       </c>
-      <c r="C91" s="21" t="n">
+      <c r="C91" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="D91" s="20" t="n">
-        <v>-239300</v>
-      </c>
-      <c r="E91" s="17" t="n">
+      <c r="D91" s="24" t="n">
+        <v>115990</v>
+      </c>
+      <c r="E91" s="25" t="n">
+        <v>0.3835646000824572</v>
+      </c>
+      <c r="F91" s="26" t="n">
+        <v>-52890</v>
+      </c>
+      <c r="G91" s="27" t="n">
         <v>63100</v>
       </c>
-      <c r="F91" s="18" t="n">
+      <c r="H91" s="28" t="n">
         <v>0.2086630712067436</v>
       </c>
+      <c r="I91" s="29" t="n">
+        <v>-17.49015288757137</v>
+      </c>
     </row>
     <row r="92" hidden="1" outlineLevel="4">
-      <c r="A92" s="22" t="inlineStr">
+      <c r="A92" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B92" s="20" t="n">
+      <c r="B92" s="31" t="n">
         <v>302400</v>
       </c>
-      <c r="C92" s="21" t="n">
+      <c r="C92" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="D92" s="20" t="n">
-        <v>-239300</v>
-      </c>
-      <c r="E92" s="17" t="n">
+      <c r="D92" s="24" t="n">
+        <v>115990</v>
+      </c>
+      <c r="E92" s="25" t="n">
+        <v>0.3835646000824572</v>
+      </c>
+      <c r="F92" s="26" t="n">
+        <v>-52890</v>
+      </c>
+      <c r="G92" s="27" t="n">
         <v>63100</v>
       </c>
-      <c r="F92" s="18" t="n">
+      <c r="H92" s="28" t="n">
         <v>0.2086630712067436</v>
       </c>
+      <c r="I92" s="29" t="n">
+        <v>-17.49015288757137</v>
+      </c>
     </row>
     <row r="93" hidden="1" outlineLevel="2">
-      <c r="A93" s="14" t="inlineStr">
+      <c r="A93" s="21" t="inlineStr">
         <is>
           <t>MAS_COM</t>
         </is>
       </c>
-      <c r="B93" s="15" t="n">
+      <c r="B93" s="22" t="n">
         <v>673830</v>
       </c>
-      <c r="C93" s="16" t="n">
+      <c r="C93" s="23" t="n">
         <v>93</v>
       </c>
-      <c r="D93" s="15" t="n">
-        <v>-494554</v>
-      </c>
-      <c r="E93" s="17" t="n">
+      <c r="D93" s="24" t="n">
+        <v>288583</v>
+      </c>
+      <c r="E93" s="25" t="n">
+        <v>0.4282720158905547</v>
+      </c>
+      <c r="F93" s="26" t="n">
+        <v>-109306</v>
+      </c>
+      <c r="G93" s="27" t="n">
         <v>179276</v>
       </c>
-      <c r="F93" s="18" t="n">
+      <c r="H93" s="28" t="n">
         <v>0.2660553447922569</v>
       </c>
+      <c r="I93" s="29" t="n">
+        <v>-16.22166710982978</v>
+      </c>
     </row>
     <row r="94" hidden="1" outlineLevel="3">
-      <c r="A94" s="19" t="inlineStr">
+      <c r="A94" s="30" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="B94" s="20" t="n">
+      <c r="B94" s="31" t="n">
         <v>342630</v>
       </c>
-      <c r="C94" s="21" t="n">
+      <c r="C94" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="D94" s="20" t="n">
-        <v>-249936</v>
-      </c>
-      <c r="E94" s="17" t="n">
+      <c r="D94" s="24" t="n">
+        <v>147935</v>
+      </c>
+      <c r="E94" s="25" t="n">
+        <v>0.4317632527509071</v>
+      </c>
+      <c r="F94" s="26" t="n">
+        <v>-55241</v>
+      </c>
+      <c r="G94" s="27" t="n">
         <v>92694</v>
       </c>
-      <c r="F94" s="18" t="n">
+      <c r="H94" s="28" t="n">
         <v>0.2705371520588912</v>
       </c>
+      <c r="I94" s="29" t="n">
+        <v>-16.12261006920159</v>
+      </c>
     </row>
     <row r="95" hidden="1" outlineLevel="4">
-      <c r="A95" s="22" t="inlineStr">
+      <c r="A95" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B95" s="20" t="n">
+      <c r="B95" s="31" t="n">
         <v>342630</v>
       </c>
-      <c r="C95" s="21" t="n">
+      <c r="C95" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="D95" s="20" t="n">
-        <v>-249936</v>
-      </c>
-      <c r="E95" s="17" t="n">
+      <c r="D95" s="24" t="n">
+        <v>147935</v>
+      </c>
+      <c r="E95" s="25" t="n">
+        <v>0.4317632527509071</v>
+      </c>
+      <c r="F95" s="26" t="n">
+        <v>-55241</v>
+      </c>
+      <c r="G95" s="27" t="n">
         <v>92694</v>
       </c>
-      <c r="F95" s="18" t="n">
+      <c r="H95" s="28" t="n">
         <v>0.2705371520588912</v>
       </c>
+      <c r="I95" s="29" t="n">
+        <v>-16.12261006920159</v>
+      </c>
     </row>
     <row r="96" hidden="1" outlineLevel="3">
-      <c r="A96" s="19" t="inlineStr">
+      <c r="A96" s="30" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="B96" s="20" t="n">
+      <c r="B96" s="31" t="n">
         <v>331200</v>
       </c>
-      <c r="C96" s="21" t="n">
+      <c r="C96" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D96" s="20" t="n">
-        <v>-244618</v>
-      </c>
-      <c r="E96" s="17" t="n">
+      <c r="D96" s="24" t="n">
+        <v>140647</v>
+      </c>
+      <c r="E96" s="25" t="n">
+        <v>0.4246602934102934</v>
+      </c>
+      <c r="F96" s="26" t="n">
+        <v>-54066</v>
+      </c>
+      <c r="G96" s="27" t="n">
         <v>86582</v>
       </c>
-      <c r="F96" s="18" t="n">
+      <c r="H96" s="28" t="n">
         <v>0.2614188664596274</v>
       </c>
+      <c r="I96" s="29" t="n">
+        <v>-16.32414269506661</v>
+      </c>
     </row>
     <row r="97" hidden="1" outlineLevel="4">
-      <c r="A97" s="22" t="inlineStr">
+      <c r="A97" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B97" s="20" t="n">
+      <c r="B97" s="31" t="n">
         <v>331200</v>
       </c>
-      <c r="C97" s="21" t="n">
+      <c r="C97" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D97" s="20" t="n">
-        <v>-244618</v>
-      </c>
-      <c r="E97" s="17" t="n">
+      <c r="D97" s="24" t="n">
+        <v>140647</v>
+      </c>
+      <c r="E97" s="25" t="n">
+        <v>0.4246602934102934</v>
+      </c>
+      <c r="F97" s="26" t="n">
+        <v>-54066</v>
+      </c>
+      <c r="G97" s="27" t="n">
         <v>86582</v>
       </c>
-      <c r="F97" s="18" t="n">
+      <c r="H97" s="28" t="n">
         <v>0.2614188664596274</v>
+      </c>
+      <c r="I97" s="29" t="n">
+        <v>-16.32414269506661</v>
       </c>
     </row>
     <row r="98">
@@ -2725,542 +3649,767 @@
       <c r="C98" s="7" t="n">
         <v>379</v>
       </c>
-      <c r="D98" s="6" t="n">
-        <v>-2144860</v>
-      </c>
-      <c r="E98" s="6" t="n">
+      <c r="D98" s="8" t="n">
+        <v>883393</v>
+      </c>
+      <c r="E98" s="9" t="n">
+        <v>0.3420291931237417</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>-445453</v>
+      </c>
+      <c r="G98" s="6" t="n">
         <v>437940</v>
       </c>
-      <c r="F98" s="8" t="n">
-        <v>0.1695600875549878</v>
+      <c r="H98" s="11" t="n">
+        <v>0.1695600875549877</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>-17.2469105568754</v>
       </c>
     </row>
     <row r="99" hidden="1" outlineLevel="1">
-      <c r="A99" s="9" t="inlineStr">
+      <c r="A99" s="13" t="inlineStr">
         <is>
           <t>Montpellier</t>
         </is>
       </c>
-      <c r="B99" s="10" t="n">
+      <c r="B99" s="14" t="n">
         <v>781650</v>
       </c>
-      <c r="C99" s="11" t="n">
+      <c r="C99" s="15" t="n">
         <v>117</v>
       </c>
-      <c r="D99" s="10" t="n">
-        <v>-665433</v>
-      </c>
-      <c r="E99" s="12" t="n">
+      <c r="D99" s="14" t="n">
+        <v>253732</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0.3246107592912429</v>
+      </c>
+      <c r="F99" s="17" t="n">
+        <v>-137515</v>
+      </c>
+      <c r="G99" s="18" t="n">
         <v>116217</v>
       </c>
-      <c r="F99" s="13" t="n">
-        <v>0.148682174805551</v>
+      <c r="H99" s="19" t="n">
+        <v>0.1486821748055509</v>
+      </c>
+      <c r="I99" s="20" t="n">
+        <v>-17.5928584485692</v>
       </c>
     </row>
     <row r="100" hidden="1" outlineLevel="2">
-      <c r="A100" s="14" t="inlineStr">
+      <c r="A100" s="21" t="inlineStr">
         <is>
           <t>BAC_CCE</t>
         </is>
       </c>
-      <c r="B100" s="15" t="n">
+      <c r="B100" s="22" t="n">
         <v>781650</v>
       </c>
-      <c r="C100" s="16" t="n">
+      <c r="C100" s="23" t="n">
         <v>117</v>
       </c>
-      <c r="D100" s="15" t="n">
-        <v>-665433</v>
-      </c>
-      <c r="E100" s="17" t="n">
+      <c r="D100" s="24" t="n">
+        <v>253732</v>
+      </c>
+      <c r="E100" s="25" t="n">
+        <v>0.3246107592912429</v>
+      </c>
+      <c r="F100" s="26" t="n">
+        <v>-137515</v>
+      </c>
+      <c r="G100" s="27" t="n">
         <v>116217</v>
       </c>
-      <c r="F100" s="18" t="n">
-        <v>0.148682174805551</v>
+      <c r="H100" s="28" t="n">
+        <v>0.1486821748055509</v>
+      </c>
+      <c r="I100" s="29" t="n">
+        <v>-17.5928584485692</v>
       </c>
     </row>
     <row r="101" hidden="1" outlineLevel="3">
-      <c r="A101" s="19" t="inlineStr">
+      <c r="A101" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B101" s="20" t="n">
+      <c r="B101" s="31" t="n">
         <v>269600</v>
       </c>
-      <c r="C101" s="21" t="n">
+      <c r="C101" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="D101" s="20" t="n">
-        <v>-227498</v>
-      </c>
-      <c r="E101" s="17" t="n">
+      <c r="D101" s="24" t="n">
+        <v>89115</v>
+      </c>
+      <c r="E101" s="25" t="n">
+        <v>0.3305460447893682</v>
+      </c>
+      <c r="F101" s="26" t="n">
+        <v>-47014</v>
+      </c>
+      <c r="G101" s="27" t="n">
         <v>42102</v>
       </c>
-      <c r="F101" s="18" t="n">
+      <c r="H101" s="28" t="n">
         <v>0.1561635115483005</v>
       </c>
+      <c r="I101" s="29" t="n">
+        <v>-17.43825332410676</v>
+      </c>
     </row>
     <row r="102" hidden="1" outlineLevel="4">
-      <c r="A102" s="22" t="inlineStr">
+      <c r="A102" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B102" s="20" t="n">
+      <c r="B102" s="31" t="n">
         <v>269600</v>
       </c>
-      <c r="C102" s="21" t="n">
+      <c r="C102" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="D102" s="20" t="n">
-        <v>-227498</v>
-      </c>
-      <c r="E102" s="17" t="n">
+      <c r="D102" s="24" t="n">
+        <v>89115</v>
+      </c>
+      <c r="E102" s="25" t="n">
+        <v>0.3305460447893682</v>
+      </c>
+      <c r="F102" s="26" t="n">
+        <v>-47014</v>
+      </c>
+      <c r="G102" s="27" t="n">
         <v>42102</v>
       </c>
-      <c r="F102" s="18" t="n">
+      <c r="H102" s="28" t="n">
         <v>0.1561635115483005</v>
       </c>
+      <c r="I102" s="29" t="n">
+        <v>-17.43825332410676</v>
+      </c>
     </row>
     <row r="103" hidden="1" outlineLevel="3">
-      <c r="A103" s="19" t="inlineStr">
+      <c r="A103" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B103" s="20" t="n">
+      <c r="B103" s="31" t="n">
         <v>259350</v>
       </c>
-      <c r="C103" s="21" t="n">
+      <c r="C103" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="D103" s="20" t="n">
-        <v>-221811</v>
-      </c>
-      <c r="E103" s="17" t="n">
+      <c r="D103" s="24" t="n">
+        <v>83377</v>
+      </c>
+      <c r="E103" s="25" t="n">
+        <v>0.3214857656962921</v>
+      </c>
+      <c r="F103" s="26" t="n">
+        <v>-45838</v>
+      </c>
+      <c r="G103" s="27" t="n">
         <v>37539</v>
       </c>
-      <c r="F103" s="18" t="n">
+      <c r="H103" s="28" t="n">
         <v>0.1447431680955709</v>
       </c>
+      <c r="I103" s="29" t="n">
+        <v>-17.67425976007212</v>
+      </c>
     </row>
     <row r="104" hidden="1" outlineLevel="4">
-      <c r="A104" s="22" t="inlineStr">
+      <c r="A104" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B104" s="20" t="n">
+      <c r="B104" s="31" t="n">
         <v>259350</v>
       </c>
-      <c r="C104" s="21" t="n">
+      <c r="C104" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="D104" s="20" t="n">
-        <v>-221811</v>
-      </c>
-      <c r="E104" s="17" t="n">
+      <c r="D104" s="24" t="n">
+        <v>83377</v>
+      </c>
+      <c r="E104" s="25" t="n">
+        <v>0.3214857656962921</v>
+      </c>
+      <c r="F104" s="26" t="n">
+        <v>-45838</v>
+      </c>
+      <c r="G104" s="27" t="n">
         <v>37539</v>
       </c>
-      <c r="F104" s="18" t="n">
+      <c r="H104" s="28" t="n">
         <v>0.1447431680955709</v>
       </c>
+      <c r="I104" s="29" t="n">
+        <v>-17.67425976007212</v>
+      </c>
     </row>
     <row r="105" hidden="1" outlineLevel="3">
-      <c r="A105" s="19" t="inlineStr">
+      <c r="A105" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B105" s="20" t="n">
+      <c r="B105" s="31" t="n">
         <v>252700</v>
       </c>
-      <c r="C105" s="21" t="n">
+      <c r="C105" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="D105" s="20" t="n">
-        <v>-216123</v>
-      </c>
-      <c r="E105" s="17" t="n">
+      <c r="D105" s="24" t="n">
+        <v>81239</v>
+      </c>
+      <c r="E105" s="25" t="n">
+        <v>0.3214857656962921</v>
+      </c>
+      <c r="F105" s="26" t="n">
+        <v>-44663</v>
+      </c>
+      <c r="G105" s="27" t="n">
         <v>36577</v>
       </c>
-      <c r="F105" s="18" t="n">
+      <c r="H105" s="28" t="n">
         <v>0.1447431680955709</v>
       </c>
+      <c r="I105" s="29" t="n">
+        <v>-17.67425976007212</v>
+      </c>
     </row>
     <row r="106" hidden="1" outlineLevel="4">
-      <c r="A106" s="22" t="inlineStr">
+      <c r="A106" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B106" s="20" t="n">
+      <c r="B106" s="31" t="n">
         <v>252700</v>
       </c>
-      <c r="C106" s="21" t="n">
+      <c r="C106" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="D106" s="20" t="n">
-        <v>-216123</v>
-      </c>
-      <c r="E106" s="17" t="n">
+      <c r="D106" s="24" t="n">
+        <v>81239</v>
+      </c>
+      <c r="E106" s="25" t="n">
+        <v>0.3214857656962921</v>
+      </c>
+      <c r="F106" s="26" t="n">
+        <v>-44663</v>
+      </c>
+      <c r="G106" s="27" t="n">
         <v>36577</v>
       </c>
-      <c r="F106" s="18" t="n">
+      <c r="H106" s="28" t="n">
         <v>0.1447431680955709</v>
       </c>
+      <c r="I106" s="29" t="n">
+        <v>-17.67425976007212</v>
+      </c>
     </row>
     <row r="107" hidden="1" outlineLevel="1">
-      <c r="A107" s="9" t="inlineStr">
+      <c r="A107" s="13" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="B107" s="10" t="n">
+      <c r="B107" s="14" t="n">
         <v>1019500</v>
       </c>
-      <c r="C107" s="11" t="n">
+      <c r="C107" s="15" t="n">
         <v>145</v>
       </c>
-      <c r="D107" s="10" t="n">
-        <v>-814240</v>
-      </c>
-      <c r="E107" s="12" t="n">
+      <c r="D107" s="14" t="n">
+        <v>375684</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>0.3684982834722904</v>
+      </c>
+      <c r="F107" s="17" t="n">
+        <v>-170424</v>
+      </c>
+      <c r="G107" s="18" t="n">
         <v>205260</v>
       </c>
-      <c r="F107" s="13" t="n">
+      <c r="H107" s="19" t="n">
         <v>0.201333938463467</v>
       </c>
+      <c r="I107" s="20" t="n">
+        <v>-16.71643450088234</v>
+      </c>
     </row>
     <row r="108" hidden="1" outlineLevel="2">
-      <c r="A108" s="14" t="inlineStr">
+      <c r="A108" s="21" t="inlineStr">
         <is>
           <t>BAC_CCE</t>
         </is>
       </c>
-      <c r="B108" s="15" t="n">
+      <c r="B108" s="22" t="n">
         <v>1019500</v>
       </c>
-      <c r="C108" s="16" t="n">
+      <c r="C108" s="23" t="n">
         <v>145</v>
       </c>
-      <c r="D108" s="15" t="n">
-        <v>-814240</v>
-      </c>
-      <c r="E108" s="17" t="n">
+      <c r="D108" s="24" t="n">
+        <v>375684</v>
+      </c>
+      <c r="E108" s="25" t="n">
+        <v>0.3684982834722904</v>
+      </c>
+      <c r="F108" s="26" t="n">
+        <v>-170424</v>
+      </c>
+      <c r="G108" s="27" t="n">
         <v>205260</v>
       </c>
-      <c r="F108" s="18" t="n">
+      <c r="H108" s="28" t="n">
         <v>0.201333938463467</v>
       </c>
+      <c r="I108" s="29" t="n">
+        <v>-16.71643450088234</v>
+      </c>
     </row>
     <row r="109" hidden="1" outlineLevel="3">
-      <c r="A109" s="19" t="inlineStr">
+      <c r="A109" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B109" s="20" t="n">
+      <c r="B109" s="31" t="n">
         <v>354500</v>
       </c>
-      <c r="C109" s="21" t="n">
+      <c r="C109" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="D109" s="20" t="n">
-        <v>-280772</v>
-      </c>
-      <c r="E109" s="17" t="n">
+      <c r="D109" s="24" t="n">
+        <v>132494</v>
+      </c>
+      <c r="E109" s="25" t="n">
+        <v>0.3737503039735421</v>
+      </c>
+      <c r="F109" s="26" t="n">
+        <v>-58767</v>
+      </c>
+      <c r="G109" s="27" t="n">
         <v>73728</v>
       </c>
-      <c r="F109" s="18" t="n">
-        <v>0.2079762173663777</v>
+      <c r="H109" s="28" t="n">
+        <v>0.2079762173663776</v>
+      </c>
+      <c r="I109" s="29" t="n">
+        <v>-16.57740866071644</v>
       </c>
     </row>
     <row r="110" hidden="1" outlineLevel="4">
-      <c r="A110" s="22" t="inlineStr">
+      <c r="A110" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B110" s="20" t="n">
+      <c r="B110" s="31" t="n">
         <v>354500</v>
       </c>
-      <c r="C110" s="21" t="n">
+      <c r="C110" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="D110" s="20" t="n">
-        <v>-280772</v>
-      </c>
-      <c r="E110" s="17" t="n">
+      <c r="D110" s="24" t="n">
+        <v>132494</v>
+      </c>
+      <c r="E110" s="25" t="n">
+        <v>0.3737503039735421</v>
+      </c>
+      <c r="F110" s="26" t="n">
+        <v>-58767</v>
+      </c>
+      <c r="G110" s="27" t="n">
         <v>73728</v>
       </c>
-      <c r="F110" s="18" t="n">
-        <v>0.2079762173663777</v>
+      <c r="H110" s="28" t="n">
+        <v>0.2079762173663776</v>
+      </c>
+      <c r="I110" s="29" t="n">
+        <v>-16.57740866071644</v>
       </c>
     </row>
     <row r="111" hidden="1" outlineLevel="3">
-      <c r="A111" s="19" t="inlineStr">
+      <c r="A111" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B111" s="20" t="n">
+      <c r="B111" s="31" t="n">
         <v>336000</v>
       </c>
-      <c r="C111" s="21" t="n">
+      <c r="C111" s="32" t="n">
         <v>48</v>
       </c>
-      <c r="D111" s="20" t="n">
-        <v>-269542</v>
-      </c>
-      <c r="E111" s="17" t="n">
+      <c r="D111" s="24" t="n">
+        <v>122875</v>
+      </c>
+      <c r="E111" s="25" t="n">
+        <v>0.3656985221674877</v>
+      </c>
+      <c r="F111" s="26" t="n">
+        <v>-56416</v>
+      </c>
+      <c r="G111" s="27" t="n">
         <v>66458</v>
       </c>
-      <c r="F111" s="18" t="n">
-        <v>0.1977930544468025</v>
+      <c r="H111" s="28" t="n">
+        <v>0.1977930544468026</v>
+      </c>
+      <c r="I111" s="29" t="n">
+        <v>-16.79054677206851</v>
       </c>
     </row>
     <row r="112" hidden="1" outlineLevel="4">
-      <c r="A112" s="22" t="inlineStr">
+      <c r="A112" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B112" s="20" t="n">
+      <c r="B112" s="31" t="n">
         <v>336000</v>
       </c>
-      <c r="C112" s="21" t="n">
+      <c r="C112" s="32" t="n">
         <v>48</v>
       </c>
-      <c r="D112" s="20" t="n">
-        <v>-269542</v>
-      </c>
-      <c r="E112" s="17" t="n">
+      <c r="D112" s="24" t="n">
+        <v>122875</v>
+      </c>
+      <c r="E112" s="25" t="n">
+        <v>0.3656985221674877</v>
+      </c>
+      <c r="F112" s="26" t="n">
+        <v>-56416</v>
+      </c>
+      <c r="G112" s="27" t="n">
         <v>66458</v>
       </c>
-      <c r="F112" s="18" t="n">
-        <v>0.1977930544468025</v>
+      <c r="H112" s="28" t="n">
+        <v>0.1977930544468026</v>
+      </c>
+      <c r="I112" s="29" t="n">
+        <v>-16.79054677206851</v>
       </c>
     </row>
     <row r="113" hidden="1" outlineLevel="3">
-      <c r="A113" s="19" t="inlineStr">
+      <c r="A113" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B113" s="20" t="n">
+      <c r="B113" s="31" t="n">
         <v>329000</v>
       </c>
-      <c r="C113" s="21" t="n">
+      <c r="C113" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="D113" s="20" t="n">
-        <v>-263926</v>
-      </c>
-      <c r="E113" s="17" t="n">
+      <c r="D113" s="24" t="n">
+        <v>120315</v>
+      </c>
+      <c r="E113" s="25" t="n">
+        <v>0.3656985221674878</v>
+      </c>
+      <c r="F113" s="26" t="n">
+        <v>-55241</v>
+      </c>
+      <c r="G113" s="27" t="n">
         <v>65074</v>
       </c>
-      <c r="F113" s="18" t="n">
-        <v>0.1977930544468027</v>
+      <c r="H113" s="28" t="n">
+        <v>0.1977930544468026</v>
+      </c>
+      <c r="I113" s="29" t="n">
+        <v>-16.79054677206851</v>
       </c>
     </row>
     <row r="114" hidden="1" outlineLevel="4">
-      <c r="A114" s="22" t="inlineStr">
+      <c r="A114" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B114" s="20" t="n">
+      <c r="B114" s="31" t="n">
         <v>329000</v>
       </c>
-      <c r="C114" s="21" t="n">
+      <c r="C114" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="D114" s="20" t="n">
-        <v>-263926</v>
-      </c>
-      <c r="E114" s="17" t="n">
+      <c r="D114" s="24" t="n">
+        <v>120315</v>
+      </c>
+      <c r="E114" s="25" t="n">
+        <v>0.3656985221674878</v>
+      </c>
+      <c r="F114" s="26" t="n">
+        <v>-55241</v>
+      </c>
+      <c r="G114" s="27" t="n">
         <v>65074</v>
       </c>
-      <c r="F114" s="18" t="n">
-        <v>0.1977930544468027</v>
+      <c r="H114" s="28" t="n">
+        <v>0.1977930544468026</v>
+      </c>
+      <c r="I114" s="29" t="n">
+        <v>-16.79054677206851</v>
       </c>
     </row>
     <row r="115" hidden="1" outlineLevel="1">
-      <c r="A115" s="9" t="inlineStr">
+      <c r="A115" s="13" t="inlineStr">
         <is>
           <t>Rennes</t>
         </is>
       </c>
-      <c r="B115" s="10" t="n">
+      <c r="B115" s="14" t="n">
         <v>781650</v>
       </c>
-      <c r="C115" s="11" t="n">
+      <c r="C115" s="15" t="n">
         <v>117</v>
       </c>
-      <c r="D115" s="10" t="n">
-        <v>-665188</v>
-      </c>
-      <c r="E115" s="12" t="n">
+      <c r="D115" s="14" t="n">
+        <v>253977</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>0.3249241988102092</v>
+      </c>
+      <c r="F115" s="17" t="n">
+        <v>-137515</v>
+      </c>
+      <c r="G115" s="18" t="n">
         <v>116462</v>
       </c>
-      <c r="F115" s="13" t="n">
-        <v>0.1489956143245171</v>
+      <c r="H115" s="19" t="n">
+        <v>0.1489956143245172</v>
+      </c>
+      <c r="I115" s="20" t="n">
+        <v>-17.5928584485692</v>
       </c>
     </row>
     <row r="116" hidden="1" outlineLevel="2">
-      <c r="A116" s="14" t="inlineStr">
+      <c r="A116" s="21" t="inlineStr">
         <is>
           <t>BAC_CCE</t>
         </is>
       </c>
-      <c r="B116" s="15" t="n">
+      <c r="B116" s="22" t="n">
         <v>781650</v>
       </c>
-      <c r="C116" s="16" t="n">
+      <c r="C116" s="23" t="n">
         <v>117</v>
       </c>
-      <c r="D116" s="15" t="n">
-        <v>-665188</v>
-      </c>
-      <c r="E116" s="17" t="n">
+      <c r="D116" s="24" t="n">
+        <v>253977</v>
+      </c>
+      <c r="E116" s="25" t="n">
+        <v>0.3249241988102092</v>
+      </c>
+      <c r="F116" s="26" t="n">
+        <v>-137515</v>
+      </c>
+      <c r="G116" s="27" t="n">
         <v>116462</v>
       </c>
-      <c r="F116" s="18" t="n">
-        <v>0.1489956143245171</v>
+      <c r="H116" s="28" t="n">
+        <v>0.1489956143245172</v>
+      </c>
+      <c r="I116" s="29" t="n">
+        <v>-17.5928584485692</v>
       </c>
     </row>
     <row r="117" hidden="1" outlineLevel="3">
-      <c r="A117" s="19" t="inlineStr">
+      <c r="A117" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B117" s="20" t="n">
+      <c r="B117" s="31" t="n">
         <v>269600</v>
       </c>
-      <c r="C117" s="21" t="n">
+      <c r="C117" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="D117" s="20" t="n">
-        <v>-227415</v>
-      </c>
-      <c r="E117" s="17" t="n">
+      <c r="D117" s="24" t="n">
+        <v>89199</v>
+      </c>
+      <c r="E117" s="25" t="n">
+        <v>0.3308567298181541</v>
+      </c>
+      <c r="F117" s="26" t="n">
+        <v>-47014</v>
+      </c>
+      <c r="G117" s="27" t="n">
         <v>42185</v>
       </c>
-      <c r="F117" s="18" t="n">
-        <v>0.1564741965770864</v>
+      <c r="H117" s="28" t="n">
+        <v>0.1564741965770865</v>
+      </c>
+      <c r="I117" s="29" t="n">
+        <v>-17.43825332410676</v>
       </c>
     </row>
     <row r="118" hidden="1" outlineLevel="4">
-      <c r="A118" s="22" t="inlineStr">
+      <c r="A118" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B118" s="20" t="n">
+      <c r="B118" s="31" t="n">
         <v>269600</v>
       </c>
-      <c r="C118" s="21" t="n">
+      <c r="C118" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="D118" s="20" t="n">
-        <v>-227415</v>
-      </c>
-      <c r="E118" s="17" t="n">
+      <c r="D118" s="24" t="n">
+        <v>89199</v>
+      </c>
+      <c r="E118" s="25" t="n">
+        <v>0.3308567298181541</v>
+      </c>
+      <c r="F118" s="26" t="n">
+        <v>-47014</v>
+      </c>
+      <c r="G118" s="27" t="n">
         <v>42185</v>
       </c>
-      <c r="F118" s="18" t="n">
-        <v>0.1564741965770864</v>
+      <c r="H118" s="28" t="n">
+        <v>0.1564741965770865</v>
+      </c>
+      <c r="I118" s="29" t="n">
+        <v>-17.43825332410676</v>
       </c>
     </row>
     <row r="119" hidden="1" outlineLevel="3">
-      <c r="A119" s="19" t="inlineStr">
+      <c r="A119" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B119" s="20" t="n">
+      <c r="B119" s="31" t="n">
         <v>259350</v>
       </c>
-      <c r="C119" s="21" t="n">
+      <c r="C119" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="D119" s="20" t="n">
-        <v>-221729</v>
-      </c>
-      <c r="E119" s="17" t="n">
+      <c r="D119" s="24" t="n">
+        <v>83459</v>
+      </c>
+      <c r="E119" s="25" t="n">
+        <v>0.321800655484866</v>
+      </c>
+      <c r="F119" s="26" t="n">
+        <v>-45838</v>
+      </c>
+      <c r="G119" s="27" t="n">
         <v>37621</v>
       </c>
-      <c r="F119" s="18" t="n">
+      <c r="H119" s="28" t="n">
         <v>0.1450580578841448</v>
       </c>
+      <c r="I119" s="29" t="n">
+        <v>-17.67425976007212</v>
+      </c>
     </row>
     <row r="120" hidden="1" outlineLevel="4">
-      <c r="A120" s="22" t="inlineStr">
+      <c r="A120" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B120" s="20" t="n">
+      <c r="B120" s="31" t="n">
         <v>259350</v>
       </c>
-      <c r="C120" s="21" t="n">
+      <c r="C120" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="D120" s="20" t="n">
-        <v>-221729</v>
-      </c>
-      <c r="E120" s="17" t="n">
+      <c r="D120" s="24" t="n">
+        <v>83459</v>
+      </c>
+      <c r="E120" s="25" t="n">
+        <v>0.321800655484866</v>
+      </c>
+      <c r="F120" s="26" t="n">
+        <v>-45838</v>
+      </c>
+      <c r="G120" s="27" t="n">
         <v>37621</v>
       </c>
-      <c r="F120" s="18" t="n">
+      <c r="H120" s="28" t="n">
         <v>0.1450580578841448</v>
       </c>
+      <c r="I120" s="29" t="n">
+        <v>-17.67425976007212</v>
+      </c>
     </row>
     <row r="121" hidden="1" outlineLevel="3">
-      <c r="A121" s="19" t="inlineStr">
+      <c r="A121" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B121" s="20" t="n">
+      <c r="B121" s="31" t="n">
         <v>252700</v>
       </c>
-      <c r="C121" s="21" t="n">
+      <c r="C121" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="D121" s="20" t="n">
-        <v>-216044</v>
-      </c>
-      <c r="E121" s="17" t="n">
+      <c r="D121" s="24" t="n">
+        <v>81319</v>
+      </c>
+      <c r="E121" s="25" t="n">
+        <v>0.321800655484866</v>
+      </c>
+      <c r="F121" s="26" t="n">
+        <v>-44663</v>
+      </c>
+      <c r="G121" s="27" t="n">
         <v>36656</v>
       </c>
-      <c r="F121" s="18" t="n">
+      <c r="H121" s="28" t="n">
         <v>0.1450580578841448</v>
       </c>
+      <c r="I121" s="29" t="n">
+        <v>-17.67425976007212</v>
+      </c>
     </row>
     <row r="122" hidden="1" outlineLevel="4">
-      <c r="A122" s="22" t="inlineStr">
+      <c r="A122" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B122" s="20" t="n">
+      <c r="B122" s="31" t="n">
         <v>252700</v>
       </c>
-      <c r="C122" s="21" t="n">
+      <c r="C122" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="D122" s="20" t="n">
-        <v>-216044</v>
-      </c>
-      <c r="E122" s="17" t="n">
+      <c r="D122" s="24" t="n">
+        <v>81319</v>
+      </c>
+      <c r="E122" s="25" t="n">
+        <v>0.321800655484866</v>
+      </c>
+      <c r="F122" s="26" t="n">
+        <v>-44663</v>
+      </c>
+      <c r="G122" s="27" t="n">
         <v>36656</v>
       </c>
-      <c r="F122" s="18" t="n">
+      <c r="H122" s="28" t="n">
         <v>0.1450580578841448</v>
+      </c>
+      <c r="I122" s="29" t="n">
+        <v>-17.67425976007212</v>
       </c>
     </row>
     <row r="123">
@@ -3275,498 +4424,705 @@
       <c r="C123" s="7" t="n">
         <v>324</v>
       </c>
-      <c r="D123" s="6" t="n">
-        <v>-2080707</v>
-      </c>
-      <c r="E123" s="27" t="n">
+      <c r="D123" s="8" t="n">
+        <v>452323</v>
+      </c>
+      <c r="E123" s="9" t="n">
+        <v>0.2101657823085001</v>
+      </c>
+      <c r="F123" s="10" t="n">
+        <v>-380810</v>
+      </c>
+      <c r="G123" s="38" t="n">
         <v>71513</v>
       </c>
-      <c r="F123" s="28" t="n">
-        <v>0.03322773657408912</v>
+      <c r="H123" s="39" t="n">
+        <v>0.03322773657408915</v>
+      </c>
+      <c r="I123" s="12" t="n">
+        <v>-17.69380457344109</v>
       </c>
     </row>
     <row r="124" hidden="1" outlineLevel="1">
-      <c r="A124" s="9" t="inlineStr">
+      <c r="A124" s="13" t="inlineStr">
         <is>
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="B124" s="10" t="n">
+      <c r="B124" s="14" t="n">
         <v>901790</v>
       </c>
-      <c r="C124" s="11" t="n">
+      <c r="C124" s="15" t="n">
         <v>142</v>
       </c>
-      <c r="D124" s="10" t="n">
-        <v>-945991</v>
-      </c>
-      <c r="E124" s="25" t="n">
+      <c r="D124" s="14" t="n">
+        <v>122697</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>0.136059392985063</v>
+      </c>
+      <c r="F124" s="17" t="n">
+        <v>-166898</v>
+      </c>
+      <c r="G124" s="36" t="n">
         <v>-44201</v>
       </c>
-      <c r="F124" s="26" t="n">
-        <v>-0.04901477607243492</v>
+      <c r="H124" s="37" t="n">
+        <v>-0.04901477607243485</v>
+      </c>
+      <c r="I124" s="20" t="n">
+        <v>-18.50741690574979</v>
       </c>
     </row>
     <row r="125" hidden="1" outlineLevel="2">
-      <c r="A125" s="14" t="inlineStr">
+      <c r="A125" s="21" t="inlineStr">
         <is>
           <t>BAC_RH</t>
         </is>
       </c>
-      <c r="B125" s="15" t="n">
+      <c r="B125" s="22" t="n">
         <v>485330</v>
       </c>
-      <c r="C125" s="16" t="n">
+      <c r="C125" s="23" t="n">
         <v>71</v>
       </c>
-      <c r="D125" s="15" t="n">
-        <v>-472996</v>
-      </c>
-      <c r="E125" s="23" t="n">
+      <c r="D125" s="24" t="n">
+        <v>95784</v>
+      </c>
+      <c r="E125" s="25" t="n">
+        <v>0.1973574681144788</v>
+      </c>
+      <c r="F125" s="26" t="n">
+        <v>-83449</v>
+      </c>
+      <c r="G125" s="34" t="n">
         <v>12334</v>
       </c>
-      <c r="F125" s="24" t="n">
-        <v>0.02541463033980891</v>
+      <c r="H125" s="35" t="n">
+        <v>0.02541463033980897</v>
+      </c>
+      <c r="I125" s="29" t="n">
+        <v>-17.19428377746698</v>
       </c>
     </row>
     <row r="126" hidden="1" outlineLevel="3">
-      <c r="A126" s="19" t="inlineStr">
+      <c r="A126" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B126" s="20" t="n">
+      <c r="B126" s="31" t="n">
         <v>247680</v>
       </c>
-      <c r="C126" s="21" t="n">
+      <c r="C126" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="D126" s="20" t="n">
-        <v>-239829</v>
-      </c>
-      <c r="E126" s="23" t="n">
+      <c r="D126" s="24" t="n">
+        <v>50163</v>
+      </c>
+      <c r="E126" s="25" t="n">
+        <v>0.2025333688175566</v>
+      </c>
+      <c r="F126" s="26" t="n">
+        <v>-42312</v>
+      </c>
+      <c r="G126" s="34" t="n">
         <v>7851</v>
       </c>
-      <c r="F126" s="24" t="n">
-        <v>0.03169931735755721</v>
+      <c r="H126" s="35" t="n">
+        <v>0.03169931735755718</v>
+      </c>
+      <c r="I126" s="29" t="n">
+        <v>-17.08340514599994</v>
       </c>
     </row>
     <row r="127" hidden="1" outlineLevel="4">
-      <c r="A127" s="22" t="inlineStr">
+      <c r="A127" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B127" s="20" t="n">
+      <c r="B127" s="31" t="n">
         <v>247680</v>
       </c>
-      <c r="C127" s="21" t="n">
+      <c r="C127" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="D127" s="20" t="n">
-        <v>-239829</v>
-      </c>
-      <c r="E127" s="23" t="n">
+      <c r="D127" s="24" t="n">
+        <v>50163</v>
+      </c>
+      <c r="E127" s="25" t="n">
+        <v>0.2025333688175566</v>
+      </c>
+      <c r="F127" s="26" t="n">
+        <v>-42312</v>
+      </c>
+      <c r="G127" s="34" t="n">
         <v>7851</v>
       </c>
-      <c r="F127" s="24" t="n">
-        <v>0.03169931735755721</v>
+      <c r="H127" s="35" t="n">
+        <v>0.03169931735755718</v>
+      </c>
+      <c r="I127" s="29" t="n">
+        <v>-17.08340514599994</v>
       </c>
     </row>
     <row r="128" hidden="1" outlineLevel="3">
-      <c r="A128" s="19" t="inlineStr">
+      <c r="A128" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B128" s="20" t="n">
+      <c r="B128" s="31" t="n">
         <v>237650</v>
       </c>
-      <c r="C128" s="21" t="n">
+      <c r="C128" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="D128" s="20" t="n">
-        <v>-233167</v>
-      </c>
-      <c r="E128" s="23" t="n">
+      <c r="D128" s="24" t="n">
+        <v>45620</v>
+      </c>
+      <c r="E128" s="25" t="n">
+        <v>0.1919631189197037</v>
+      </c>
+      <c r="F128" s="26" t="n">
+        <v>-41137</v>
+      </c>
+      <c r="G128" s="34" t="n">
         <v>4483</v>
       </c>
-      <c r="F128" s="24" t="n">
-        <v>0.01886469858910044</v>
+      <c r="H128" s="35" t="n">
+        <v>0.0188646985891005</v>
+      </c>
+      <c r="I128" s="29" t="n">
+        <v>-17.30984203306032</v>
       </c>
     </row>
     <row r="129" hidden="1" outlineLevel="4">
-      <c r="A129" s="22" t="inlineStr">
+      <c r="A129" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B129" s="20" t="n">
+      <c r="B129" s="31" t="n">
         <v>237650</v>
       </c>
-      <c r="C129" s="21" t="n">
+      <c r="C129" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="D129" s="20" t="n">
-        <v>-233167</v>
-      </c>
-      <c r="E129" s="23" t="n">
+      <c r="D129" s="24" t="n">
+        <v>45620</v>
+      </c>
+      <c r="E129" s="25" t="n">
+        <v>0.1919631189197037</v>
+      </c>
+      <c r="F129" s="26" t="n">
+        <v>-41137</v>
+      </c>
+      <c r="G129" s="34" t="n">
         <v>4483</v>
       </c>
-      <c r="F129" s="24" t="n">
-        <v>0.01886469858910044</v>
+      <c r="H129" s="35" t="n">
+        <v>0.0188646985891005</v>
+      </c>
+      <c r="I129" s="29" t="n">
+        <v>-17.30984203306032</v>
       </c>
     </row>
     <row r="130" hidden="1" outlineLevel="2">
-      <c r="A130" s="14" t="inlineStr">
+      <c r="A130" s="21" t="inlineStr">
         <is>
           <t>BTS_GES</t>
         </is>
       </c>
-      <c r="B130" s="15" t="n">
+      <c r="B130" s="22" t="n">
         <v>416460</v>
       </c>
-      <c r="C130" s="16" t="n">
+      <c r="C130" s="23" t="n">
         <v>71</v>
       </c>
-      <c r="D130" s="15" t="n">
-        <v>-472996</v>
-      </c>
-      <c r="E130" s="23" t="n">
+      <c r="D130" s="24" t="n">
+        <v>26914</v>
+      </c>
+      <c r="E130" s="25" t="n">
+        <v>0.06462445372904961</v>
+      </c>
+      <c r="F130" s="26" t="n">
+        <v>-83449</v>
+      </c>
+      <c r="G130" s="34" t="n">
         <v>-56536</v>
       </c>
-      <c r="F130" s="24" t="n">
-        <v>-0.1357525751745199</v>
+      <c r="H130" s="35" t="n">
+        <v>-0.1357525751745198</v>
+      </c>
+      <c r="I130" s="29" t="n">
+        <v>-20.03770289035694</v>
       </c>
     </row>
     <row r="131" hidden="1" outlineLevel="3">
-      <c r="A131" s="19" t="inlineStr">
+      <c r="A131" s="30" t="inlineStr">
         <is>
           <t>BTS1</t>
         </is>
       </c>
-      <c r="B131" s="20" t="n">
+      <c r="B131" s="31" t="n">
         <v>212760</v>
       </c>
-      <c r="C131" s="21" t="n">
+      <c r="C131" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="D131" s="20" t="n">
-        <v>-239829</v>
-      </c>
-      <c r="E131" s="23" t="n">
+      <c r="D131" s="24" t="n">
+        <v>15243</v>
+      </c>
+      <c r="E131" s="25" t="n">
+        <v>0.07164629060317922</v>
+      </c>
+      <c r="F131" s="26" t="n">
+        <v>-42312</v>
+      </c>
+      <c r="G131" s="34" t="n">
         <v>-27069</v>
       </c>
-      <c r="F131" s="24" t="n">
+      <c r="H131" s="35" t="n">
         <v>-0.1272265138037236</v>
       </c>
+      <c r="I131" s="29" t="n">
+        <v>-19.88728044069029</v>
+      </c>
     </row>
     <row r="132" hidden="1" outlineLevel="4">
-      <c r="A132" s="22" t="inlineStr">
+      <c r="A132" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B132" s="20" t="n">
+      <c r="B132" s="31" t="n">
         <v>212760</v>
       </c>
-      <c r="C132" s="21" t="n">
+      <c r="C132" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="D132" s="20" t="n">
-        <v>-239829</v>
-      </c>
-      <c r="E132" s="23" t="n">
+      <c r="D132" s="24" t="n">
+        <v>15243</v>
+      </c>
+      <c r="E132" s="25" t="n">
+        <v>0.07164629060317922</v>
+      </c>
+      <c r="F132" s="26" t="n">
+        <v>-42312</v>
+      </c>
+      <c r="G132" s="34" t="n">
         <v>-27069</v>
       </c>
-      <c r="F132" s="24" t="n">
+      <c r="H132" s="35" t="n">
         <v>-0.1272265138037236</v>
       </c>
+      <c r="I132" s="29" t="n">
+        <v>-19.88728044069029</v>
+      </c>
     </row>
     <row r="133" hidden="1" outlineLevel="3">
-      <c r="A133" s="19" t="inlineStr">
+      <c r="A133" s="30" t="inlineStr">
         <is>
           <t>BTS2</t>
         </is>
       </c>
-      <c r="B133" s="20" t="n">
+      <c r="B133" s="31" t="n">
         <v>203700</v>
       </c>
-      <c r="C133" s="21" t="n">
+      <c r="C133" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="D133" s="20" t="n">
-        <v>-233167</v>
-      </c>
-      <c r="E133" s="23" t="n">
+      <c r="D133" s="24" t="n">
+        <v>11670</v>
+      </c>
+      <c r="E133" s="25" t="n">
+        <v>0.05729030540632101</v>
+      </c>
+      <c r="F133" s="26" t="n">
+        <v>-41137</v>
+      </c>
+      <c r="G133" s="34" t="n">
         <v>-29467</v>
       </c>
-      <c r="F133" s="24" t="n">
-        <v>-0.1446578516460495</v>
+      <c r="H133" s="35" t="n">
+        <v>-0.1446578516460494</v>
+      </c>
+      <c r="I133" s="29" t="n">
+        <v>-20.19481570523704</v>
       </c>
     </row>
     <row r="134" hidden="1" outlineLevel="4">
-      <c r="A134" s="22" t="inlineStr">
+      <c r="A134" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B134" s="20" t="n">
+      <c r="B134" s="31" t="n">
         <v>203700</v>
       </c>
-      <c r="C134" s="21" t="n">
+      <c r="C134" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="D134" s="20" t="n">
-        <v>-233167</v>
-      </c>
-      <c r="E134" s="23" t="n">
+      <c r="D134" s="24" t="n">
+        <v>11670</v>
+      </c>
+      <c r="E134" s="25" t="n">
+        <v>0.05729030540632101</v>
+      </c>
+      <c r="F134" s="26" t="n">
+        <v>-41137</v>
+      </c>
+      <c r="G134" s="34" t="n">
         <v>-29467</v>
       </c>
-      <c r="F134" s="24" t="n">
-        <v>-0.1446578516460495</v>
+      <c r="H134" s="35" t="n">
+        <v>-0.1446578516460494</v>
+      </c>
+      <c r="I134" s="29" t="n">
+        <v>-20.19481570523704</v>
       </c>
     </row>
     <row r="135" hidden="1" outlineLevel="1">
-      <c r="A135" s="9" t="inlineStr">
+      <c r="A135" s="13" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="B135" s="10" t="n">
+      <c r="B135" s="14" t="n">
         <v>1250430</v>
       </c>
-      <c r="C135" s="11" t="n">
+      <c r="C135" s="15" t="n">
         <v>182</v>
       </c>
-      <c r="D135" s="10" t="n">
-        <v>-1134716</v>
-      </c>
-      <c r="E135" s="12" t="n">
+      <c r="D135" s="14" t="n">
+        <v>329626</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>0.263610118119367</v>
+      </c>
+      <c r="F135" s="17" t="n">
+        <v>-213912</v>
+      </c>
+      <c r="G135" s="18" t="n">
         <v>115714</v>
       </c>
-      <c r="F135" s="13" t="n">
+      <c r="H135" s="19" t="n">
         <v>0.09253971363758641</v>
       </c>
+      <c r="I135" s="20" t="n">
+        <v>-17.10704044817806</v>
+      </c>
     </row>
     <row r="136" hidden="1" outlineLevel="2">
-      <c r="A136" s="14" t="inlineStr">
+      <c r="A136" s="21" t="inlineStr">
         <is>
           <t>BAC_RH</t>
         </is>
       </c>
-      <c r="B136" s="15" t="n">
+      <c r="B136" s="22" t="n">
         <v>672990</v>
       </c>
-      <c r="C136" s="16" t="n">
+      <c r="C136" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="D136" s="15" t="n">
-        <v>-567358</v>
-      </c>
-      <c r="E136" s="17" t="n">
+      <c r="D136" s="24" t="n">
+        <v>212588</v>
+      </c>
+      <c r="E136" s="25" t="n">
+        <v>0.3158858229691378</v>
+      </c>
+      <c r="F136" s="26" t="n">
+        <v>-106956</v>
+      </c>
+      <c r="G136" s="27" t="n">
         <v>105632</v>
       </c>
-      <c r="F136" s="18" t="n">
+      <c r="H136" s="28" t="n">
         <v>0.1569595641271395</v>
       </c>
+      <c r="I136" s="29" t="n">
+        <v>-15.89262588419983</v>
+      </c>
     </row>
     <row r="137" hidden="1" outlineLevel="3">
-      <c r="A137" s="19" t="inlineStr">
+      <c r="A137" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B137" s="20" t="n">
+      <c r="B137" s="31" t="n">
         <v>342240</v>
       </c>
-      <c r="C137" s="21" t="n">
+      <c r="C137" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D137" s="20" t="n">
-        <v>-286796</v>
-      </c>
-      <c r="E137" s="17" t="n">
+      <c r="D137" s="24" t="n">
+        <v>109509</v>
+      </c>
+      <c r="E137" s="25" t="n">
+        <v>0.3199781401394305</v>
+      </c>
+      <c r="F137" s="26" t="n">
+        <v>-54066</v>
+      </c>
+      <c r="G137" s="27" t="n">
         <v>55444</v>
       </c>
-      <c r="F137" s="18" t="n">
+      <c r="H137" s="28" t="n">
         <v>0.162002565671044</v>
       </c>
+      <c r="I137" s="29" t="n">
+        <v>-15.79755744683865</v>
+      </c>
     </row>
     <row r="138" hidden="1" outlineLevel="4">
-      <c r="A138" s="22" t="inlineStr">
+      <c r="A138" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B138" s="20" t="n">
+      <c r="B138" s="31" t="n">
         <v>342240</v>
       </c>
-      <c r="C138" s="21" t="n">
+      <c r="C138" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D138" s="20" t="n">
-        <v>-286796</v>
-      </c>
-      <c r="E138" s="17" t="n">
+      <c r="D138" s="24" t="n">
+        <v>109509</v>
+      </c>
+      <c r="E138" s="25" t="n">
+        <v>0.3199781401394305</v>
+      </c>
+      <c r="F138" s="26" t="n">
+        <v>-54066</v>
+      </c>
+      <c r="G138" s="27" t="n">
         <v>55444</v>
       </c>
-      <c r="F138" s="18" t="n">
+      <c r="H138" s="28" t="n">
         <v>0.162002565671044</v>
       </c>
+      <c r="I138" s="29" t="n">
+        <v>-15.79755744683865</v>
+      </c>
     </row>
     <row r="139" hidden="1" outlineLevel="3">
-      <c r="A139" s="19" t="inlineStr">
+      <c r="A139" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B139" s="20" t="n">
+      <c r="B139" s="31" t="n">
         <v>330750</v>
       </c>
-      <c r="C139" s="21" t="n">
+      <c r="C139" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="D139" s="20" t="n">
-        <v>-280562</v>
-      </c>
-      <c r="E139" s="17" t="n">
+      <c r="D139" s="24" t="n">
+        <v>103079</v>
+      </c>
+      <c r="E139" s="25" t="n">
+        <v>0.3116513418554235</v>
+      </c>
+      <c r="F139" s="26" t="n">
+        <v>-52890</v>
+      </c>
+      <c r="G139" s="27" t="n">
         <v>50188</v>
       </c>
-      <c r="F139" s="18" t="n">
-        <v>0.151741372597628</v>
+      <c r="H139" s="28" t="n">
+        <v>0.1517413725976281</v>
+      </c>
+      <c r="I139" s="29" t="n">
+        <v>-15.99099692577954</v>
       </c>
     </row>
     <row r="140" hidden="1" outlineLevel="4">
-      <c r="A140" s="22" t="inlineStr">
+      <c r="A140" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B140" s="20" t="n">
+      <c r="B140" s="31" t="n">
         <v>330750</v>
       </c>
-      <c r="C140" s="21" t="n">
+      <c r="C140" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="D140" s="20" t="n">
-        <v>-280562</v>
-      </c>
-      <c r="E140" s="17" t="n">
+      <c r="D140" s="24" t="n">
+        <v>103079</v>
+      </c>
+      <c r="E140" s="25" t="n">
+        <v>0.3116513418554235</v>
+      </c>
+      <c r="F140" s="26" t="n">
+        <v>-52890</v>
+      </c>
+      <c r="G140" s="27" t="n">
         <v>50188</v>
       </c>
-      <c r="F140" s="18" t="n">
-        <v>0.151741372597628</v>
+      <c r="H140" s="28" t="n">
+        <v>0.1517413725976281</v>
+      </c>
+      <c r="I140" s="29" t="n">
+        <v>-15.99099692577954</v>
       </c>
     </row>
     <row r="141" hidden="1" outlineLevel="2">
-      <c r="A141" s="14" t="inlineStr">
+      <c r="A141" s="21" t="inlineStr">
         <is>
           <t>BTS_GES</t>
         </is>
       </c>
-      <c r="B141" s="15" t="n">
+      <c r="B141" s="22" t="n">
         <v>577440</v>
       </c>
-      <c r="C141" s="16" t="n">
+      <c r="C141" s="23" t="n">
         <v>91</v>
       </c>
-      <c r="D141" s="15" t="n">
-        <v>-567358</v>
-      </c>
-      <c r="E141" s="23" t="n">
+      <c r="D141" s="24" t="n">
+        <v>117038</v>
+      </c>
+      <c r="E141" s="25" t="n">
+        <v>0.2026842615683015</v>
+      </c>
+      <c r="F141" s="26" t="n">
+        <v>-106956</v>
+      </c>
+      <c r="G141" s="34" t="n">
         <v>10082</v>
       </c>
-      <c r="F141" s="24" t="n">
+      <c r="H141" s="35" t="n">
         <v>0.01746019856941601</v>
       </c>
+      <c r="I141" s="29" t="n">
+        <v>-18.52240629988854</v>
+      </c>
     </row>
     <row r="142" hidden="1" outlineLevel="3">
-      <c r="A142" s="19" t="inlineStr">
+      <c r="A142" s="30" t="inlineStr">
         <is>
           <t>BTS1</t>
         </is>
       </c>
-      <c r="B142" s="20" t="n">
+      <c r="B142" s="31" t="n">
         <v>293940</v>
       </c>
-      <c r="C142" s="21" t="n">
+      <c r="C142" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D142" s="20" t="n">
-        <v>-286796</v>
-      </c>
-      <c r="E142" s="23" t="n">
+      <c r="D142" s="24" t="n">
+        <v>61209</v>
+      </c>
+      <c r="E142" s="25" t="n">
+        <v>0.2082374589416843</v>
+      </c>
+      <c r="F142" s="26" t="n">
+        <v>-54066</v>
+      </c>
+      <c r="G142" s="34" t="n">
         <v>7144</v>
       </c>
-      <c r="F142" s="24" t="n">
-        <v>0.02430345674375081</v>
+      <c r="H142" s="35" t="n">
+        <v>0.02430345674375071</v>
+      </c>
+      <c r="I142" s="29" t="n">
+        <v>-18.39340021979336</v>
       </c>
     </row>
     <row r="143" hidden="1" outlineLevel="4">
-      <c r="A143" s="22" t="inlineStr">
+      <c r="A143" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B143" s="20" t="n">
+      <c r="B143" s="31" t="n">
         <v>293940</v>
       </c>
-      <c r="C143" s="21" t="n">
+      <c r="C143" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D143" s="20" t="n">
-        <v>-286796</v>
-      </c>
-      <c r="E143" s="23" t="n">
+      <c r="D143" s="24" t="n">
+        <v>61209</v>
+      </c>
+      <c r="E143" s="25" t="n">
+        <v>0.2082374589416843</v>
+      </c>
+      <c r="F143" s="26" t="n">
+        <v>-54066</v>
+      </c>
+      <c r="G143" s="34" t="n">
         <v>7144</v>
       </c>
-      <c r="F143" s="24" t="n">
-        <v>0.02430345674375081</v>
+      <c r="H143" s="35" t="n">
+        <v>0.02430345674375071</v>
+      </c>
+      <c r="I143" s="29" t="n">
+        <v>-18.39340021979336</v>
       </c>
     </row>
     <row r="144" hidden="1" outlineLevel="3">
-      <c r="A144" s="19" t="inlineStr">
+      <c r="A144" s="30" t="inlineStr">
         <is>
           <t>BTS2</t>
         </is>
       </c>
-      <c r="B144" s="20" t="n">
+      <c r="B144" s="31" t="n">
         <v>283500</v>
       </c>
-      <c r="C144" s="21" t="n">
+      <c r="C144" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="D144" s="20" t="n">
-        <v>-280562</v>
-      </c>
-      <c r="E144" s="23" t="n">
+      <c r="D144" s="24" t="n">
+        <v>55829</v>
+      </c>
+      <c r="E144" s="25" t="n">
+        <v>0.196926565497994</v>
+      </c>
+      <c r="F144" s="26" t="n">
+        <v>-52890</v>
+      </c>
+      <c r="G144" s="34" t="n">
         <v>2938</v>
       </c>
-      <c r="F144" s="24" t="n">
-        <v>0.0103649346972327</v>
+      <c r="H144" s="35" t="n">
+        <v>0.01036493469723281</v>
+      </c>
+      <c r="I144" s="29" t="n">
+        <v>-18.65616308007612</v>
       </c>
     </row>
     <row r="145" hidden="1" outlineLevel="4">
-      <c r="A145" s="22" t="inlineStr">
+      <c r="A145" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B145" s="20" t="n">
+      <c r="B145" s="31" t="n">
         <v>283500</v>
       </c>
-      <c r="C145" s="21" t="n">
+      <c r="C145" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="D145" s="20" t="n">
-        <v>-280562</v>
-      </c>
-      <c r="E145" s="23" t="n">
+      <c r="D145" s="24" t="n">
+        <v>55829</v>
+      </c>
+      <c r="E145" s="25" t="n">
+        <v>0.196926565497994</v>
+      </c>
+      <c r="F145" s="26" t="n">
+        <v>-52890</v>
+      </c>
+      <c r="G145" s="34" t="n">
         <v>2938</v>
       </c>
-      <c r="F145" s="24" t="n">
-        <v>0.0103649346972327</v>
+      <c r="H145" s="35" t="n">
+        <v>0.01036493469723281</v>
+      </c>
+      <c r="I145" s="29" t="n">
+        <v>-18.65616308007612</v>
       </c>
     </row>
     <row r="146">
@@ -3781,401 +5137,563 @@
       <c r="C146" s="7" t="n">
         <v>255</v>
       </c>
-      <c r="D146" s="6" t="n">
-        <v>-1878371</v>
-      </c>
-      <c r="E146" s="27" t="n">
+      <c r="D146" s="8" t="n">
+        <v>371040</v>
+      </c>
+      <c r="E146" s="9" t="n">
+        <v>0.1903062009539929</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>-299711</v>
+      </c>
+      <c r="G146" s="38" t="n">
         <v>71329</v>
       </c>
-      <c r="F146" s="28" t="n">
-        <v>0.03658446946636772</v>
+      <c r="H146" s="39" t="n">
+        <v>0.03658446946636766</v>
+      </c>
+      <c r="I146" s="12" t="n">
+        <v>-15.37217314876252</v>
       </c>
     </row>
     <row r="147" hidden="1" outlineLevel="1">
-      <c r="A147" s="9" t="inlineStr">
+      <c r="A147" s="13" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="B147" s="10" t="n">
+      <c r="B147" s="14" t="n">
         <v>863550</v>
       </c>
-      <c r="C147" s="11" t="n">
+      <c r="C147" s="15" t="n">
         <v>117</v>
       </c>
-      <c r="D147" s="10" t="n">
-        <v>-777313</v>
-      </c>
-      <c r="E147" s="12" t="n">
+      <c r="D147" s="14" t="n">
+        <v>223752</v>
+      </c>
+      <c r="E147" s="16" t="n">
+        <v>0.2591071738752823</v>
+      </c>
+      <c r="F147" s="17" t="n">
+        <v>-137515</v>
+      </c>
+      <c r="G147" s="18" t="n">
         <v>86237</v>
       </c>
-      <c r="F147" s="13" t="n">
-        <v>0.09986384336374143</v>
+      <c r="H147" s="19" t="n">
+        <v>0.09986384336374139</v>
+      </c>
+      <c r="I147" s="20" t="n">
+        <v>-15.92433305115409</v>
       </c>
     </row>
     <row r="148" hidden="1" outlineLevel="2">
-      <c r="A148" s="14" t="inlineStr">
+      <c r="A148" s="21" t="inlineStr">
         <is>
           <t>BAC_TOU</t>
         </is>
       </c>
-      <c r="B148" s="15" t="n">
+      <c r="B148" s="22" t="n">
         <v>863550</v>
       </c>
-      <c r="C148" s="16" t="n">
+      <c r="C148" s="23" t="n">
         <v>117</v>
       </c>
-      <c r="D148" s="15" t="n">
-        <v>-777313</v>
-      </c>
-      <c r="E148" s="17" t="n">
+      <c r="D148" s="24" t="n">
+        <v>223752</v>
+      </c>
+      <c r="E148" s="25" t="n">
+        <v>0.2591071738752823</v>
+      </c>
+      <c r="F148" s="26" t="n">
+        <v>-137515</v>
+      </c>
+      <c r="G148" s="27" t="n">
         <v>86237</v>
       </c>
-      <c r="F148" s="18" t="n">
-        <v>0.09986384336374143</v>
+      <c r="H148" s="28" t="n">
+        <v>0.09986384336374139</v>
+      </c>
+      <c r="I148" s="29" t="n">
+        <v>-15.92433305115409</v>
       </c>
     </row>
     <row r="149" hidden="1" outlineLevel="3">
-      <c r="A149" s="19" t="inlineStr">
+      <c r="A149" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B149" s="20" t="n">
+      <c r="B149" s="31" t="n">
         <v>297600</v>
       </c>
-      <c r="C149" s="21" t="n">
+      <c r="C149" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="D149" s="20" t="n">
-        <v>-265748</v>
-      </c>
-      <c r="E149" s="17" t="n">
+      <c r="D149" s="24" t="n">
+        <v>78866</v>
+      </c>
+      <c r="E149" s="25" t="n">
+        <v>0.2650055141990626</v>
+      </c>
+      <c r="F149" s="26" t="n">
+        <v>-47014</v>
+      </c>
+      <c r="G149" s="27" t="n">
         <v>31852</v>
       </c>
-      <c r="F149" s="18" t="n">
+      <c r="H149" s="28" t="n">
         <v>0.1070299397306761</v>
       </c>
+      <c r="I149" s="29" t="n">
+        <v>-15.79755744683865</v>
+      </c>
     </row>
     <row r="150" hidden="1" outlineLevel="4">
-      <c r="A150" s="22" t="inlineStr">
+      <c r="A150" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B150" s="20" t="n">
+      <c r="B150" s="31" t="n">
         <v>297600</v>
       </c>
-      <c r="C150" s="21" t="n">
+      <c r="C150" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="D150" s="20" t="n">
-        <v>-265748</v>
-      </c>
-      <c r="E150" s="17" t="n">
+      <c r="D150" s="24" t="n">
+        <v>78866</v>
+      </c>
+      <c r="E150" s="25" t="n">
+        <v>0.2650055141990626</v>
+      </c>
+      <c r="F150" s="26" t="n">
+        <v>-47014</v>
+      </c>
+      <c r="G150" s="27" t="n">
         <v>31852</v>
       </c>
-      <c r="F150" s="18" t="n">
+      <c r="H150" s="28" t="n">
         <v>0.1070299397306761</v>
       </c>
+      <c r="I150" s="29" t="n">
+        <v>-15.79755744683865</v>
+      </c>
     </row>
     <row r="151" hidden="1" outlineLevel="3">
-      <c r="A151" s="19" t="inlineStr">
+      <c r="A151" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B151" s="20" t="n">
+      <c r="B151" s="31" t="n">
         <v>286650</v>
       </c>
-      <c r="C151" s="21" t="n">
+      <c r="C151" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="D151" s="20" t="n">
-        <v>-259104</v>
-      </c>
-      <c r="E151" s="17" t="n">
+      <c r="D151" s="24" t="n">
+        <v>73384</v>
+      </c>
+      <c r="E151" s="25" t="n">
+        <v>0.2560055817198674</v>
+      </c>
+      <c r="F151" s="26" t="n">
+        <v>-45838</v>
+      </c>
+      <c r="G151" s="27" t="n">
         <v>27546</v>
       </c>
-      <c r="F151" s="18" t="n">
+      <c r="H151" s="28" t="n">
         <v>0.09609561246207207</v>
       </c>
+      <c r="I151" s="29" t="n">
+        <v>-15.99099692577954</v>
+      </c>
     </row>
     <row r="152" hidden="1" outlineLevel="4">
-      <c r="A152" s="22" t="inlineStr">
+      <c r="A152" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B152" s="20" t="n">
+      <c r="B152" s="31" t="n">
         <v>286650</v>
       </c>
-      <c r="C152" s="21" t="n">
+      <c r="C152" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="D152" s="20" t="n">
-        <v>-259104</v>
-      </c>
-      <c r="E152" s="17" t="n">
+      <c r="D152" s="24" t="n">
+        <v>73384</v>
+      </c>
+      <c r="E152" s="25" t="n">
+        <v>0.2560055817198674</v>
+      </c>
+      <c r="F152" s="26" t="n">
+        <v>-45838</v>
+      </c>
+      <c r="G152" s="27" t="n">
         <v>27546</v>
       </c>
-      <c r="F152" s="18" t="n">
+      <c r="H152" s="28" t="n">
         <v>0.09609561246207207</v>
       </c>
+      <c r="I152" s="29" t="n">
+        <v>-15.99099692577954</v>
+      </c>
     </row>
     <row r="153" hidden="1" outlineLevel="3">
-      <c r="A153" s="19" t="inlineStr">
+      <c r="A153" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B153" s="20" t="n">
+      <c r="B153" s="31" t="n">
         <v>279300</v>
       </c>
-      <c r="C153" s="21" t="n">
+      <c r="C153" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="D153" s="20" t="n">
-        <v>-252460</v>
-      </c>
-      <c r="E153" s="17" t="n">
+      <c r="D153" s="24" t="n">
+        <v>71502</v>
+      </c>
+      <c r="E153" s="25" t="n">
+        <v>0.2560055817198674</v>
+      </c>
+      <c r="F153" s="26" t="n">
+        <v>-44663</v>
+      </c>
+      <c r="G153" s="27" t="n">
         <v>26840</v>
       </c>
-      <c r="F153" s="18" t="n">
+      <c r="H153" s="28" t="n">
         <v>0.09609561246207207</v>
       </c>
+      <c r="I153" s="29" t="n">
+        <v>-15.99099692577954</v>
+      </c>
     </row>
     <row r="154" hidden="1" outlineLevel="4">
-      <c r="A154" s="22" t="inlineStr">
+      <c r="A154" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B154" s="20" t="n">
+      <c r="B154" s="31" t="n">
         <v>279300</v>
       </c>
-      <c r="C154" s="21" t="n">
+      <c r="C154" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="D154" s="20" t="n">
-        <v>-252460</v>
-      </c>
-      <c r="E154" s="17" t="n">
+      <c r="D154" s="24" t="n">
+        <v>71502</v>
+      </c>
+      <c r="E154" s="25" t="n">
+        <v>0.2560055817198674</v>
+      </c>
+      <c r="F154" s="26" t="n">
+        <v>-44663</v>
+      </c>
+      <c r="G154" s="27" t="n">
         <v>26840</v>
       </c>
-      <c r="F154" s="18" t="n">
+      <c r="H154" s="28" t="n">
         <v>0.09609561246207207</v>
       </c>
+      <c r="I154" s="29" t="n">
+        <v>-15.99099692577954</v>
+      </c>
     </row>
     <row r="155" hidden="1" outlineLevel="1">
-      <c r="A155" s="9" t="inlineStr">
+      <c r="A155" s="13" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="B155" s="10" t="n">
+      <c r="B155" s="14" t="n">
         <v>1086150</v>
       </c>
-      <c r="C155" s="11" t="n">
+      <c r="C155" s="15" t="n">
         <v>138</v>
       </c>
-      <c r="D155" s="10" t="n">
-        <v>-1101059</v>
-      </c>
-      <c r="E155" s="25" t="n">
+      <c r="D155" s="14" t="n">
+        <v>147288</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0.1356055793398702</v>
+      </c>
+      <c r="F155" s="17" t="n">
+        <v>-162197</v>
+      </c>
+      <c r="G155" s="36" t="n">
         <v>-14909</v>
       </c>
-      <c r="F155" s="26" t="n">
-        <v>-0.01372617209241969</v>
+      <c r="H155" s="37" t="n">
+        <v>-0.01372617209241985</v>
+      </c>
+      <c r="I155" s="20" t="n">
+        <v>-14.933175143229</v>
       </c>
     </row>
     <row r="156" hidden="1" outlineLevel="2">
-      <c r="A156" s="14" t="inlineStr">
+      <c r="A156" s="21" t="inlineStr">
         <is>
           <t>BAC_TOU</t>
         </is>
       </c>
-      <c r="B156" s="15" t="n">
+      <c r="B156" s="22" t="n">
         <v>1086150</v>
       </c>
-      <c r="C156" s="16" t="n">
+      <c r="C156" s="23" t="n">
         <v>138</v>
       </c>
-      <c r="D156" s="15" t="n">
-        <v>-1101059</v>
-      </c>
-      <c r="E156" s="23" t="n">
+      <c r="D156" s="24" t="n">
+        <v>147288</v>
+      </c>
+      <c r="E156" s="25" t="n">
+        <v>0.1356055793398702</v>
+      </c>
+      <c r="F156" s="26" t="n">
+        <v>-162197</v>
+      </c>
+      <c r="G156" s="34" t="n">
         <v>-14909</v>
       </c>
-      <c r="F156" s="24" t="n">
-        <v>-0.01372617209241969</v>
+      <c r="H156" s="35" t="n">
+        <v>-0.01372617209241985</v>
+      </c>
+      <c r="I156" s="29" t="n">
+        <v>-14.933175143229</v>
       </c>
     </row>
     <row r="157" hidden="1" outlineLevel="3">
-      <c r="A157" s="19" t="inlineStr">
+      <c r="A157" s="30" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B157" s="20" t="n">
+      <c r="B157" s="31" t="n">
         <v>372710</v>
       </c>
-      <c r="C157" s="21" t="n">
+      <c r="C157" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="D157" s="20" t="n">
-        <v>-374998</v>
-      </c>
-      <c r="E157" s="23" t="n">
+      <c r="D157" s="24" t="n">
+        <v>52953</v>
+      </c>
+      <c r="E157" s="25" t="n">
+        <v>0.1420746751466637</v>
+      </c>
+      <c r="F157" s="26" t="n">
+        <v>-55241</v>
+      </c>
+      <c r="G157" s="34" t="n">
         <v>-2288</v>
       </c>
-      <c r="F157" s="24" t="n">
-        <v>-0.00613948299265483</v>
+      <c r="H157" s="35" t="n">
+        <v>-0.006139482992654811</v>
+      </c>
+      <c r="I157" s="29" t="n">
+        <v>-14.82141581393185</v>
       </c>
     </row>
     <row r="158" hidden="1" outlineLevel="4">
-      <c r="A158" s="22" t="inlineStr">
+      <c r="A158" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B158" s="20" t="n">
+      <c r="B158" s="31" t="n">
         <v>372710</v>
       </c>
-      <c r="C158" s="21" t="n">
+      <c r="C158" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="D158" s="20" t="n">
-        <v>-374998</v>
-      </c>
-      <c r="E158" s="23" t="n">
+      <c r="D158" s="24" t="n">
+        <v>52953</v>
+      </c>
+      <c r="E158" s="25" t="n">
+        <v>0.1420746751466637</v>
+      </c>
+      <c r="F158" s="26" t="n">
+        <v>-55241</v>
+      </c>
+      <c r="G158" s="34" t="n">
         <v>-2288</v>
       </c>
-      <c r="F158" s="24" t="n">
-        <v>-0.00613948299265483</v>
+      <c r="H158" s="35" t="n">
+        <v>-0.006139482992654811</v>
+      </c>
+      <c r="I158" s="29" t="n">
+        <v>-14.82141581393185</v>
       </c>
     </row>
     <row r="159" hidden="1" outlineLevel="3">
-      <c r="A159" s="19" t="inlineStr">
+      <c r="A159" s="30" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="B159" s="20" t="n">
+      <c r="B159" s="31" t="n">
         <v>360640</v>
       </c>
-      <c r="C159" s="21" t="n">
+      <c r="C159" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D159" s="20" t="n">
-        <v>-367020</v>
-      </c>
-      <c r="E159" s="23" t="n">
+      <c r="D159" s="24" t="n">
+        <v>47686</v>
+      </c>
+      <c r="E159" s="25" t="n">
+        <v>0.1322260425909494</v>
+      </c>
+      <c r="F159" s="26" t="n">
+        <v>-54066</v>
+      </c>
+      <c r="G159" s="34" t="n">
         <v>-6380</v>
       </c>
-      <c r="F159" s="24" t="n">
+      <c r="H159" s="35" t="n">
         <v>-0.01768955358823372</v>
       </c>
+      <c r="I159" s="29" t="n">
+        <v>-14.99155961791831</v>
+      </c>
     </row>
     <row r="160" hidden="1" outlineLevel="4">
-      <c r="A160" s="22" t="inlineStr">
+      <c r="A160" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B160" s="20" t="n">
+      <c r="B160" s="31" t="n">
         <v>360640</v>
       </c>
-      <c r="C160" s="21" t="n">
+      <c r="C160" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="D160" s="20" t="n">
-        <v>-367020</v>
-      </c>
-      <c r="E160" s="23" t="n">
+      <c r="D160" s="24" t="n">
+        <v>47686</v>
+      </c>
+      <c r="E160" s="25" t="n">
+        <v>0.1322260425909494</v>
+      </c>
+      <c r="F160" s="26" t="n">
+        <v>-54066</v>
+      </c>
+      <c r="G160" s="34" t="n">
         <v>-6380</v>
       </c>
-      <c r="F160" s="24" t="n">
+      <c r="H160" s="35" t="n">
         <v>-0.01768955358823372</v>
       </c>
+      <c r="I160" s="29" t="n">
+        <v>-14.99155961791831</v>
+      </c>
     </row>
     <row r="161" hidden="1" outlineLevel="3">
-      <c r="A161" s="19" t="inlineStr">
+      <c r="A161" s="30" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="B161" s="20" t="n">
+      <c r="B161" s="31" t="n">
         <v>352800</v>
       </c>
-      <c r="C161" s="21" t="n">
+      <c r="C161" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="D161" s="20" t="n">
-        <v>-359041</v>
-      </c>
-      <c r="E161" s="23" t="n">
+      <c r="D161" s="24" t="n">
+        <v>46649</v>
+      </c>
+      <c r="E161" s="25" t="n">
+        <v>0.1322260425909495</v>
+      </c>
+      <c r="F161" s="26" t="n">
+        <v>-52890</v>
+      </c>
+      <c r="G161" s="34" t="n">
         <v>-6241</v>
       </c>
-      <c r="F161" s="24" t="n">
+      <c r="H161" s="35" t="n">
         <v>-0.01768955358823366</v>
       </c>
+      <c r="I161" s="29" t="n">
+        <v>-14.99155961791831</v>
+      </c>
     </row>
     <row r="162" hidden="1" outlineLevel="4">
-      <c r="A162" s="22" t="inlineStr">
+      <c r="A162" s="33" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B162" s="20" t="n">
+      <c r="B162" s="31" t="n">
         <v>352800</v>
       </c>
-      <c r="C162" s="21" t="n">
+      <c r="C162" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="D162" s="20" t="n">
-        <v>-359041</v>
-      </c>
-      <c r="E162" s="23" t="n">
+      <c r="D162" s="24" t="n">
+        <v>46649</v>
+      </c>
+      <c r="E162" s="25" t="n">
+        <v>0.1322260425909495</v>
+      </c>
+      <c r="F162" s="26" t="n">
+        <v>-52890</v>
+      </c>
+      <c r="G162" s="34" t="n">
         <v>-6241</v>
       </c>
-      <c r="F162" s="24" t="n">
+      <c r="H162" s="35" t="n">
         <v>-0.01768955358823366</v>
       </c>
+      <c r="I162" s="29" t="n">
+        <v>-14.99155961791831</v>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="29" t="inlineStr">
+      <c r="A163" s="40" t="inlineStr">
         <is>
           <t>GROUPE</t>
         </is>
       </c>
-      <c r="B163" s="30" t="n">
+      <c r="B163" s="41" t="n">
         <v>22544725</v>
       </c>
-      <c r="C163" s="31" t="n">
+      <c r="C163" s="42" t="n">
         <v>3036</v>
       </c>
-      <c r="D163" s="30" t="n">
-        <v>-19253195</v>
-      </c>
-      <c r="E163" s="30" t="n">
+      <c r="D163" s="43" t="n">
+        <v>6859857</v>
+      </c>
+      <c r="E163" s="44" t="n">
+        <v>0.3042776968891836</v>
+      </c>
+      <c r="F163" s="45" t="n">
+        <v>-3568327</v>
+      </c>
+      <c r="G163" s="46" t="n">
         <v>3291530</v>
       </c>
-      <c r="F163" s="32" t="n">
+      <c r="H163" s="47" t="n">
         <v>0.1460000066534411</v>
       </c>
+      <c r="I163" s="48" t="n">
+        <v>-15.82776902357425</v>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="33" t="inlineStr">
-        <is>
-          <t>EBITDA net groupe = 3 291 530 €  (foote à la compta : 3 291 530). Coût chargé ventilé à l'effectif (3036 élèves).</t>
+      <c r="A165" s="49" t="inlineStr">
+        <is>
+          <t>EBITDA net groupe = 3 291 530 € (foote compta). EBITDA propre = avant quote-part siège ; le siège pèse 3 568 327 € réparti à l'effectif.</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="34" t="inlineStr">
-        <is>
-          <t>Rouge = marge nette &lt; 5 % : la classe ne couvre plus son coût chargé. Déplie une marque faible (Pigier/Tunon) pour voir quelles classes plombent.</t>
+      <c r="A166" s="50" t="inlineStr">
+        <is>
+          <t>Lecture : Δ (pt) = combien de points de marge le siège retire à la maille. Rouge = marge nette &lt; 5 % (la maille ne couvre plus son coût chargé).</t>
         </is>
       </c>
     </row>
